--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -748,7 +748,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -796,15 +796,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -814,13 +814,13 @@
       <c r="A8" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -828,15 +828,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -844,15 +844,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -866,7 +866,7 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -892,7 +892,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -956,15 +956,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -972,13 +972,13 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -988,7 +988,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -1004,15 +1004,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -1024,39 +1024,39 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -1070,13 +1070,13 @@
       <c r="A24" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
@@ -1100,13 +1100,13 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1132,15 +1132,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B28" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -1148,15 +1148,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -1168,31 +1168,31 @@
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1212,13 +1212,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
@@ -1308,47 +1308,47 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1374,13 +1374,13 @@
       <c r="A43" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B43" s="8" t="n"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -1394,7 +1394,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1406,13 +1406,13 @@
       <c r="A45" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B45" s="8" t="n"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -1426,7 +1426,7 @@
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1436,15 +1436,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -1470,13 +1470,13 @@
       <c r="A49" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -1484,15 +1484,15 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
@@ -1500,11 +1500,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -1582,29 +1582,29 @@
       <c r="A56" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
@@ -1630,13 +1630,13 @@
       <c r="A59" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -1646,29 +1646,29 @@
       <c r="A60" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B61" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -1676,17 +1676,17 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B62" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
@@ -1724,19 +1724,19 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B65" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -1774,13 +1774,13 @@
       <c r="A68" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -1906,13 +1906,13 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="n"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -1926,25 +1926,25 @@
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -1956,7 +1956,7 @@
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G79" s="8" t="n"/>
@@ -2060,31 +2060,31 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B86" s="8" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
@@ -2098,7 +2098,7 @@
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2114,7 +2114,7 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2128,15 +2128,15 @@
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -2322,7 +2322,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2338,7 +2338,7 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -2560,11 +2560,11 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -2672,15 +2672,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B13" s="8" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -2688,15 +2688,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -2768,13 +2768,13 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -2784,13 +2784,13 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -2816,15 +2816,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -2832,11 +2832,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -2866,33 +2866,33 @@
       <c r="A25" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2902,7 +2902,7 @@
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -2982,7 +2982,7 @@
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -3010,13 +3010,13 @@
       <c r="A34" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -3024,31 +3024,31 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -3056,31 +3056,31 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -3092,13 +3092,13 @@
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
     </row>
@@ -3106,15 +3106,15 @@
       <c r="A40" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
     </row>
@@ -3168,7 +3168,7 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
@@ -3186,13 +3186,13 @@
       <c r="A45" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B45" s="8" t="n"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -3200,15 +3200,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -3270,7 +3270,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -3286,7 +3286,7 @@
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -3296,15 +3296,15 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -3312,15 +3312,15 @@
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B53" s="8" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -3330,29 +3330,29 @@
       <c r="A54" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
@@ -3378,31 +3378,31 @@
       <c r="A57" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B58" s="8" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
     </row>
@@ -3440,31 +3440,31 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B61" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -3488,19 +3488,19 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -3522,13 +3522,13 @@
       <c r="A66" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -3542,7 +3542,7 @@
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -3558,7 +3558,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -3574,7 +3574,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -3590,7 +3590,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -3604,13 +3604,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -3626,39 +3626,39 @@
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B73" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -3672,7 +3672,7 @@
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G75" s="8" t="n"/>
@@ -3760,31 +3760,31 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
@@ -3798,7 +3798,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -3812,27 +3812,27 @@
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
+      <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -3990,7 +3990,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -4004,13 +4004,13 @@
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8" t="n"/>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
     </row>
@@ -4068,13 +4068,13 @@
       </c>
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="n"/>
     </row>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -4340,11 +4340,11 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -4372,15 +4372,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -4390,13 +4390,13 @@
       <c r="A9" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -4436,13 +4436,13 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -4452,15 +4452,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B13" s="8" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -4470,13 +4470,13 @@
       <c r="A14" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -4548,13 +4548,13 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -4568,43 +4568,43 @@
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -4612,11 +4612,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -4630,21 +4630,21 @@
       <c r="A24" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
@@ -4660,19 +4660,19 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -4740,7 +4740,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
@@ -4762,7 +4762,7 @@
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -4788,15 +4788,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -4804,7 +4804,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
@@ -4822,13 +4822,13 @@
       <c r="A36" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -4852,17 +4852,17 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="8" t="n"/>
     </row>
@@ -4884,17 +4884,17 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
     </row>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -5076,15 +5076,15 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -5092,15 +5092,15 @@
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B53" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -5110,29 +5110,29 @@
       <c r="A54" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
@@ -5158,31 +5158,31 @@
       <c r="A57" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B58" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
     </row>
@@ -5220,31 +5220,31 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B61" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -5268,19 +5268,19 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -5302,13 +5302,13 @@
       <c r="A66" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -5322,7 +5322,7 @@
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -5338,7 +5338,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -5354,7 +5354,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -5370,7 +5370,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -5384,13 +5384,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -5406,39 +5406,39 @@
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B73" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -5452,7 +5452,7 @@
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G75" s="8" t="n"/>
@@ -5540,31 +5540,31 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -5592,27 +5592,27 @@
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
+      <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -5770,7 +5770,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8" t="n"/>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
     </row>
@@ -5848,13 +5848,13 @@
       </c>
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="n"/>
     </row>
@@ -6088,7 +6088,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -6152,15 +6152,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -6170,13 +6170,13 @@
       <c r="A9" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -6216,13 +6216,13 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -6232,15 +6232,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B13" s="8" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -6250,13 +6250,13 @@
       <c r="A14" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -6328,13 +6328,13 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -6344,13 +6344,13 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -6376,15 +6376,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -6392,11 +6392,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -6410,21 +6410,21 @@
       <c r="A24" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
@@ -6440,19 +6440,19 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -6462,7 +6462,7 @@
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -6526,7 +6526,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -6536,13 +6536,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -6552,13 +6552,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -6568,15 +6568,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -6584,45 +6584,45 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B36" s="8" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -6632,17 +6632,17 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="8" t="n"/>
     </row>
@@ -6664,17 +6664,17 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
     </row>
@@ -6728,7 +6728,7 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
@@ -6746,13 +6746,13 @@
       <c r="A45" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B45" s="8" t="n"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -6760,15 +6760,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -6830,7 +6830,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -6846,7 +6846,7 @@
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -6856,15 +6856,15 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -6872,15 +6872,15 @@
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B53" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -6890,29 +6890,29 @@
       <c r="A54" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
@@ -6938,31 +6938,31 @@
       <c r="A57" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B58" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
     </row>
@@ -6984,31 +6984,31 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -7022,7 +7022,7 @@
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -7048,19 +7048,19 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -7082,13 +7082,13 @@
       <c r="A66" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -7102,7 +7102,7 @@
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -7118,7 +7118,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -7134,7 +7134,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -7150,7 +7150,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -7164,13 +7164,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -7186,39 +7186,39 @@
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B73" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -7232,7 +7232,7 @@
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G75" s="8" t="n"/>
@@ -7320,31 +7320,31 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
@@ -7358,7 +7358,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -7374,7 +7374,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -7388,15 +7388,15 @@
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -7550,7 +7550,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -7564,13 +7564,13 @@
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8" t="n"/>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
     </row>
@@ -7662,7 +7662,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -7676,13 +7676,13 @@
       </c>
       <c r="B103" s="8" t="n"/>
       <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
     </row>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -7916,15 +7916,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -7948,15 +7948,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -7986,7 +7986,7 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -7996,13 +7996,13 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -8044,15 +8044,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -8062,13 +8062,13 @@
       <c r="A16" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -8076,7 +8076,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
@@ -8130,7 +8130,7 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -8156,15 +8156,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -8172,11 +8172,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -8188,11 +8188,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -8204,15 +8204,15 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -8226,7 +8226,7 @@
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -8300,13 +8300,13 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -8354,7 +8354,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -8364,7 +8364,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
@@ -8402,29 +8402,29 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -8444,15 +8444,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -8462,13 +8462,13 @@
       <c r="A41" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -8478,13 +8478,13 @@
       <c r="A42" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -8498,7 +8498,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -8514,7 +8514,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -8524,15 +8524,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -8542,13 +8542,13 @@
       <c r="A46" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -8562,7 +8562,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -8572,15 +8572,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -8588,15 +8588,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -8606,13 +8606,13 @@
       <c r="A50" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B50" s="8" t="n"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
@@ -8636,7 +8636,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
@@ -8670,13 +8670,13 @@
       <c r="A54" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -8688,27 +8688,27 @@
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -8716,11 +8716,11 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C58" s="8" t="n"/>
@@ -8750,31 +8750,31 @@
       <c r="A59" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B60" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -8796,31 +8796,31 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B62" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -8844,19 +8844,19 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -8978,45 +8978,45 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -9024,13 +9024,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -9044,7 +9044,7 @@
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G77" s="8" t="n"/>
@@ -9148,19 +9148,19 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -9170,7 +9170,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -9186,7 +9186,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -9202,7 +9202,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -9216,15 +9216,15 @@
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -9362,7 +9362,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -9376,13 +9376,13 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
-      <c r="F98" s="8" t="n"/>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
     </row>
@@ -9440,13 +9440,13 @@
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
     </row>
@@ -9648,7 +9648,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -9696,15 +9696,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -9728,15 +9728,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -9766,7 +9766,7 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -9776,13 +9776,13 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -9824,15 +9824,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -9842,13 +9842,13 @@
       <c r="A16" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -9856,7 +9856,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
@@ -9910,7 +9910,7 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -9936,15 +9936,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -9952,11 +9952,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -9968,11 +9968,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -9984,15 +9984,15 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -10000,13 +10000,13 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -10064,7 +10064,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -10080,13 +10080,13 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -10134,7 +10134,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -10144,7 +10144,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
@@ -10176,35 +10176,35 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -10224,15 +10224,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -10242,13 +10242,13 @@
       <c r="A41" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -10258,13 +10258,13 @@
       <c r="A42" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -10278,7 +10278,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -10294,7 +10294,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -10304,15 +10304,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -10322,13 +10322,13 @@
       <c r="A46" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -10342,7 +10342,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -10352,15 +10352,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -10368,15 +10368,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -10386,13 +10386,13 @@
       <c r="A50" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B50" s="8" t="n"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
@@ -10416,7 +10416,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
@@ -10450,13 +10450,13 @@
       <c r="A54" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -10468,27 +10468,27 @@
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -10496,11 +10496,11 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C58" s="8" t="n"/>
@@ -10530,31 +10530,31 @@
       <c r="A59" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B60" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -10576,31 +10576,31 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B62" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -10624,19 +10624,19 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -10758,45 +10758,45 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -10804,13 +10804,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -10824,7 +10824,7 @@
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G77" s="8" t="n"/>
@@ -10928,19 +10928,19 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -10950,7 +10950,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -10966,7 +10966,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -10982,7 +10982,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -10996,15 +10996,15 @@
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -11142,7 +11142,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -11156,13 +11156,13 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
-      <c r="F98" s="8" t="n"/>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
     </row>
@@ -11220,13 +11220,13 @@
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
     </row>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -11476,15 +11476,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>69</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -11508,15 +11508,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -11546,7 +11546,7 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -11556,13 +11556,13 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -11604,15 +11604,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -11622,13 +11622,13 @@
       <c r="A16" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -11636,7 +11636,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
@@ -11690,7 +11690,7 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -11716,15 +11716,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -11732,11 +11732,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -11748,11 +11748,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -11764,15 +11764,15 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -11780,13 +11780,13 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -11844,7 +11844,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -11860,13 +11860,13 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -11914,7 +11914,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
@@ -11956,35 +11956,35 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -12004,15 +12004,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -12022,13 +12022,13 @@
       <c r="A41" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -12038,13 +12038,13 @@
       <c r="A42" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -12058,7 +12058,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -12074,7 +12074,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -12084,15 +12084,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -12102,13 +12102,13 @@
       <c r="A46" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -12122,7 +12122,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -12132,15 +12132,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -12148,15 +12148,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -12166,13 +12166,13 @@
       <c r="A50" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B50" s="8" t="n"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
@@ -12230,13 +12230,13 @@
       <c r="A54" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -12248,27 +12248,27 @@
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -12276,11 +12276,11 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C58" s="8" t="n"/>
@@ -12310,31 +12310,31 @@
       <c r="A59" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -12356,31 +12356,31 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B62" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -12404,19 +12404,19 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -12538,45 +12538,45 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -12584,13 +12584,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -12604,7 +12604,7 @@
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G77" s="8" t="n"/>
@@ -12922,7 +12922,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -12936,13 +12936,13 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
-      <c r="F98" s="8" t="n"/>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
     </row>
@@ -13000,13 +13000,13 @@
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
     </row>
@@ -13208,7 +13208,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -13256,15 +13256,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -13274,13 +13274,13 @@
       <c r="A8" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -13288,15 +13288,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>62</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -13304,15 +13304,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -13326,7 +13326,7 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -13432,15 +13432,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -13448,13 +13448,13 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -13464,15 +13464,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -13484,39 +13484,39 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -13530,13 +13530,13 @@
       <c r="A24" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -13544,7 +13544,7 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
@@ -13560,13 +13560,13 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -13608,7 +13608,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
@@ -13628,31 +13628,31 @@
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -13662,7 +13662,7 @@
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -13678,7 +13678,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -13688,7 +13688,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -13704,7 +13704,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
@@ -13752,31 +13752,31 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -13788,27 +13788,27 @@
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -13818,13 +13818,13 @@
       <c r="A42" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -13866,13 +13866,13 @@
       <c r="A45" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B45" s="8" t="n"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -13886,7 +13886,7 @@
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -13896,15 +13896,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -13930,13 +13930,13 @@
       <c r="A49" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -13944,15 +13944,15 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
@@ -13960,11 +13960,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -13980,7 +13980,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -14042,29 +14042,29 @@
       <c r="A56" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -14072,7 +14072,7 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
@@ -14090,25 +14090,25 @@
       <c r="A59" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -14120,17 +14120,17 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B61" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
@@ -14184,31 +14184,31 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B65" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -14232,19 +14232,19 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -14266,13 +14266,13 @@
       <c r="A70" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B70" s="8" t="n"/>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -14286,7 +14286,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -14302,7 +14302,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -14318,7 +14318,7 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -14334,7 +14334,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -14350,7 +14350,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -14364,13 +14364,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -14386,25 +14386,25 @@
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -14416,7 +14416,7 @@
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G79" s="8" t="n"/>
@@ -14504,27 +14504,27 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C86" s="8" t="n"/>
@@ -14538,13 +14538,13 @@
       <c r="A87" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
@@ -14558,7 +14558,7 @@
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -14574,7 +14574,7 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -14588,15 +14588,15 @@
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -14734,7 +14734,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -14748,13 +14748,13 @@
       </c>
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="n"/>
     </row>
@@ -14830,7 +14830,7 @@
       <c r="C105" s="8" t="n"/>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -14844,13 +14844,13 @@
       </c>
       <c r="B106" s="8" t="n"/>
       <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E106" s="8" t="n"/>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F106" s="8" t="n"/>
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="n"/>
     </row>
@@ -14988,7 +14988,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -15036,15 +15036,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>69</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -15054,13 +15054,13 @@
       <c r="A8" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -15068,15 +15068,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -15084,15 +15084,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -15106,7 +15106,7 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -15132,7 +15132,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -15196,15 +15196,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -15212,13 +15212,13 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -15228,7 +15228,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -15244,15 +15244,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -15264,39 +15264,39 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -15310,13 +15310,13 @@
       <c r="A24" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -15324,7 +15324,7 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
@@ -15340,13 +15340,13 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -15372,15 +15372,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B28" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -15390,13 +15390,13 @@
       <c r="A29" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -15404,35 +15404,35 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -15452,13 +15452,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -15468,15 +15468,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -15484,15 +15484,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -15516,7 +15516,7 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
@@ -15548,47 +15548,47 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -15596,13 +15596,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -15614,13 +15614,13 @@
       <c r="A43" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B43" s="8" t="n"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -15634,7 +15634,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -15650,7 +15650,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -15666,7 +15666,7 @@
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -15676,7 +15676,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
@@ -15710,13 +15710,13 @@
       <c r="A49" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -15724,15 +15724,15 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
@@ -15740,11 +15740,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -15822,29 +15822,29 @@
       <c r="A56" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -15852,7 +15852,7 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
@@ -15870,25 +15870,25 @@
       <c r="A59" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -15900,17 +15900,17 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
@@ -15964,31 +15964,31 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B65" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -16012,19 +16012,19 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -16046,13 +16046,13 @@
       <c r="A70" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B70" s="8" t="n"/>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -16066,7 +16066,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -16082,7 +16082,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -16098,7 +16098,7 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -16114,7 +16114,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -16130,7 +16130,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -16144,13 +16144,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -16166,25 +16166,25 @@
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -16196,7 +16196,7 @@
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G79" s="8" t="n"/>
@@ -16300,31 +16300,31 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B86" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
@@ -16338,7 +16338,7 @@
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -16354,7 +16354,7 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -16368,15 +16368,15 @@
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -16514,7 +16514,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -16528,13 +16528,13 @@
       </c>
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="n"/>
     </row>
@@ -16610,7 +16610,7 @@
       <c r="C105" s="8" t="n"/>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -16624,13 +16624,13 @@
       </c>
       <c r="B106" s="8" t="n"/>
       <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E106" s="8" t="n"/>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F106" s="8" t="n"/>
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="n"/>
     </row>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -780,13 +780,13 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -796,15 +796,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -814,13 +814,13 @@
       <c r="A8" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -844,7 +844,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -892,7 +892,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -972,15 +972,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -990,13 +990,13 @@
       <c r="A19" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -1004,17 +1004,17 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B20" s="8" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
@@ -1022,15 +1022,15 @@
       <c r="A21" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -1084,11 +1084,11 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
@@ -1100,13 +1100,13 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1122,7 +1122,7 @@
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1134,13 +1134,13 @@
       <c r="A28" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -1150,13 +1150,13 @@
       <c r="A29" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -1184,35 +1184,35 @@
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
@@ -1228,15 +1228,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -1244,15 +1244,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -1276,11 +1276,11 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
@@ -1378,7 +1378,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1388,15 +1388,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -1404,13 +1404,13 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1422,13 +1422,13 @@
       <c r="A46" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -1500,11 +1500,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -1644,11 +1644,11 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C62" s="8" t="n"/>
@@ -1810,7 +1810,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1826,7 +1826,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1842,7 +1842,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1922,13 +1922,13 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -1942,25 +1942,25 @@
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -1972,7 +1972,7 @@
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G80" s="8" t="n"/>
@@ -2322,7 +2322,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2338,7 +2338,7 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2592,15 +2592,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -2610,13 +2610,13 @@
       <c r="A9" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -2768,17 +2768,17 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
@@ -2786,21 +2786,21 @@
       <c r="A20" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -2850,45 +2850,45 @@
       <c r="A24" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -2896,15 +2896,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -2914,13 +2914,13 @@
       <c r="A28" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -2934,7 +2934,7 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -2944,15 +2944,15 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B30" s="8" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -2976,13 +2976,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -2998,7 +2998,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -3026,33 +3026,33 @@
       <c r="A35" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="8" t="n"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -3072,7 +3072,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
@@ -3200,13 +3200,13 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -3216,13 +3216,13 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -3238,7 +3238,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -3254,7 +3254,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -3314,13 +3314,13 @@
       <c r="A53" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -3332,29 +3332,29 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -3392,7 +3392,7 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
@@ -3472,15 +3472,15 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -3488,17 +3488,17 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -3522,13 +3522,13 @@
       <c r="A66" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -3538,13 +3538,13 @@
       <c r="A67" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B67" s="8" t="n"/>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -3558,7 +3558,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -3574,7 +3574,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -3590,7 +3590,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -3604,13 +3604,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -3622,13 +3622,13 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -3642,39 +3642,39 @@
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
     </row>
@@ -3688,7 +3688,7 @@
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G76" s="8" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -3730,13 +3730,13 @@
       <c r="A79" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -3750,7 +3750,7 @@
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -3764,31 +3764,31 @@
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -3798,7 +3798,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -3814,7 +3814,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -3824,15 +3824,15 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -3990,7 +3990,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -4004,31 +4004,31 @@
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C98" s="8" t="n"/>
@@ -4050,13 +4050,13 @@
       <c r="A99" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B99" s="8" t="n"/>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
@@ -4372,15 +4372,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -4390,13 +4390,13 @@
       <c r="A9" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -4436,7 +4436,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -4644,11 +4644,11 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
@@ -4662,13 +4662,13 @@
       <c r="A26" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -4676,15 +4676,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -4698,7 +4698,7 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
@@ -4724,13 +4724,13 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -4746,7 +4746,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -4756,13 +4756,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -4778,7 +4778,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -4822,13 +4822,13 @@
       <c r="A36" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
@@ -4852,15 +4852,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -4868,17 +4868,17 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
     </row>
@@ -4886,13 +4886,13 @@
       <c r="A40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -4904,13 +4904,13 @@
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
     </row>
@@ -4964,15 +4964,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -4980,13 +4980,13 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -4996,15 +4996,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B47" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -5018,7 +5018,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -5034,7 +5034,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -5044,13 +5044,13 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -5094,13 +5094,13 @@
       <c r="A53" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -5112,29 +5112,29 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
@@ -5252,15 +5252,15 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -5268,17 +5268,17 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -5302,13 +5302,13 @@
       <c r="A66" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -5318,13 +5318,13 @@
       <c r="A67" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B67" s="8" t="n"/>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -5338,7 +5338,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -5354,7 +5354,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -5370,7 +5370,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -5384,13 +5384,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -5402,13 +5402,13 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -5422,39 +5422,39 @@
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
     </row>
@@ -5468,7 +5468,7 @@
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G76" s="8" t="n"/>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -5510,13 +5510,13 @@
       <c r="A79" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -5530,7 +5530,7 @@
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -5544,31 +5544,31 @@
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -5578,7 +5578,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -5594,7 +5594,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -5604,15 +5604,15 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -5770,7 +5770,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -5784,31 +5784,31 @@
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C98" s="8" t="n"/>
@@ -5830,13 +5830,13 @@
       <c r="A99" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B99" s="8" t="n"/>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
@@ -6152,15 +6152,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -6170,13 +6170,13 @@
       <c r="A9" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -6200,15 +6200,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -6216,15 +6216,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -6328,39 +6328,39 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -6424,11 +6424,11 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
@@ -6442,13 +6442,13 @@
       <c r="A26" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -6456,15 +6456,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -6478,7 +6478,7 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -6488,13 +6488,13 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -6506,13 +6506,13 @@
       <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -6526,7 +6526,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -6536,15 +6536,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -6558,7 +6558,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -6574,7 +6574,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -6648,17 +6648,17 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
     </row>
@@ -6666,13 +6666,13 @@
       <c r="A40" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -6684,13 +6684,13 @@
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
     </row>
@@ -6760,13 +6760,13 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -6776,13 +6776,13 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -6798,7 +6798,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -6814,7 +6814,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -6874,13 +6874,13 @@
       <c r="A53" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -6892,29 +6892,29 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
@@ -7032,15 +7032,15 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -7048,17 +7048,17 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -7082,13 +7082,13 @@
       <c r="A66" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -7098,13 +7098,13 @@
       <c r="A67" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="8" t="n"/>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -7118,7 +7118,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -7134,7 +7134,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -7150,7 +7150,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -7164,13 +7164,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -7182,13 +7182,13 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -7202,39 +7202,39 @@
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
     </row>
@@ -7248,7 +7248,7 @@
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G76" s="8" t="n"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -7290,13 +7290,13 @@
       <c r="A79" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -7310,7 +7310,7 @@
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -7324,31 +7324,31 @@
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B82" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -7550,7 +7550,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -7564,31 +7564,31 @@
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C98" s="8" t="n"/>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C99" s="8" t="n"/>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C100" s="8" t="n"/>
@@ -7642,13 +7642,13 @@
       <c r="A101" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B101" s="8" t="n"/>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
@@ -7900,15 +7900,15 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B6" s="8" t="n"/>
+        <v>62</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -7916,15 +7916,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -7938,7 +7938,7 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -7964,15 +7964,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -7982,13 +7982,13 @@
       <c r="A11" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B11" s="8" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -8002,7 +8002,7 @@
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -8044,15 +8044,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -8062,13 +8062,13 @@
       <c r="A16" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -8108,15 +8108,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -8124,17 +8124,17 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
@@ -8142,15 +8142,15 @@
       <c r="A21" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -8188,11 +8188,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -8238,13 +8238,13 @@
       <c r="A27" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -8254,13 +8254,13 @@
       <c r="A28" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -8274,7 +8274,7 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -8290,7 +8290,7 @@
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -8306,7 +8306,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -8316,13 +8316,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -8332,15 +8332,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -8348,15 +8348,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -8366,13 +8366,13 @@
       <c r="A35" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="8" t="n"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -8398,13 +8398,13 @@
       <c r="A37" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -8418,29 +8418,29 @@
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -8482,7 +8482,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -8498,7 +8498,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -8514,7 +8514,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -8524,15 +8524,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -8542,13 +8542,13 @@
       <c r="A46" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -8562,7 +8562,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -8572,13 +8572,13 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -8594,7 +8594,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -8636,7 +8636,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
@@ -8830,13 +8830,13 @@
       <c r="A64" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -8844,17 +8844,17 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -8894,13 +8894,13 @@
       <c r="A68" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B68" s="8" t="n"/>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -8914,7 +8914,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -8930,7 +8930,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -8980,7 +8980,7 @@
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G73" s="8" t="n"/>
@@ -9022,13 +9022,13 @@
       <c r="A76" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -9040,13 +9040,13 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -9060,7 +9060,7 @@
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G78" s="8" t="n"/>
@@ -9362,7 +9362,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -9376,31 +9376,31 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C100" s="8" t="n"/>
@@ -9422,13 +9422,13 @@
       <c r="A101" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B101" s="8" t="n"/>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
@@ -9680,15 +9680,15 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B6" s="8" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -9696,15 +9696,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -9718,7 +9718,7 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -9744,15 +9744,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -9762,13 +9762,13 @@
       <c r="A11" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B11" s="8" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -9782,7 +9782,7 @@
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -9824,15 +9824,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -9842,13 +9842,13 @@
       <c r="A16" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -9888,15 +9888,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -9904,17 +9904,17 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
@@ -9922,15 +9922,15 @@
       <c r="A21" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -9968,11 +9968,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -10018,13 +10018,13 @@
       <c r="A27" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -10034,13 +10034,13 @@
       <c r="A28" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -10054,7 +10054,7 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -10070,7 +10070,7 @@
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -10086,7 +10086,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -10096,13 +10096,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -10112,15 +10112,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -10128,15 +10128,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -10146,13 +10146,13 @@
       <c r="A35" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="8" t="n"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -10178,13 +10178,13 @@
       <c r="A37" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -10198,29 +10198,29 @@
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -10262,7 +10262,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -10278,7 +10278,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -10294,7 +10294,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -10304,15 +10304,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -10322,13 +10322,13 @@
       <c r="A46" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -10342,7 +10342,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -10352,13 +10352,13 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -10374,7 +10374,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -10416,7 +10416,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
@@ -10610,13 +10610,13 @@
       <c r="A64" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -10624,17 +10624,17 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -10674,13 +10674,13 @@
       <c r="A68" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="8" t="n"/>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -10694,7 +10694,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -10710,7 +10710,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -10760,7 +10760,7 @@
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G73" s="8" t="n"/>
@@ -10802,13 +10802,13 @@
       <c r="A76" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -10820,13 +10820,13 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -10840,7 +10840,7 @@
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G78" s="8" t="n"/>
@@ -11142,7 +11142,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -11156,31 +11156,31 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C100" s="8" t="n"/>
@@ -11202,13 +11202,13 @@
       <c r="A101" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B101" s="8" t="n"/>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
@@ -11460,15 +11460,15 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B6" s="8" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -11476,15 +11476,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -11498,7 +11498,7 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -11524,15 +11524,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -11542,13 +11542,13 @@
       <c r="A11" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="B11" s="8" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -11562,7 +11562,7 @@
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -11604,15 +11604,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -11622,13 +11622,13 @@
       <c r="A16" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -11668,15 +11668,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -11684,17 +11684,17 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
@@ -11702,15 +11702,15 @@
       <c r="A21" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -11748,11 +11748,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -11798,13 +11798,13 @@
       <c r="A27" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -11814,13 +11814,13 @@
       <c r="A28" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -11834,7 +11834,7 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -11850,7 +11850,7 @@
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -11866,7 +11866,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -11876,13 +11876,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -11892,15 +11892,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -11908,15 +11908,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -11926,13 +11926,13 @@
       <c r="A35" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="8" t="n"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -11958,13 +11958,13 @@
       <c r="A37" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -11978,29 +11978,29 @@
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -12042,7 +12042,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -12058,7 +12058,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -12074,7 +12074,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -12084,15 +12084,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -12102,13 +12102,13 @@
       <c r="A46" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -12122,7 +12122,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -12132,13 +12132,13 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -12154,7 +12154,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
@@ -12390,13 +12390,13 @@
       <c r="A64" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -12404,17 +12404,17 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -12454,13 +12454,13 @@
       <c r="A68" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B68" s="8" t="n"/>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -12474,7 +12474,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -12490,7 +12490,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -12540,7 +12540,7 @@
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G73" s="8" t="n"/>
@@ -12582,13 +12582,13 @@
       <c r="A76" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -12600,13 +12600,13 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -12620,7 +12620,7 @@
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G78" s="8" t="n"/>
@@ -12922,7 +12922,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -12936,31 +12936,31 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C100" s="8" t="n"/>
@@ -12982,13 +12982,13 @@
       <c r="A101" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B101" s="8" t="n"/>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
@@ -13240,13 +13240,13 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -13256,15 +13256,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -13274,13 +13274,13 @@
       <c r="A8" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -13294,7 +13294,7 @@
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -13304,13 +13304,13 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -13464,17 +13464,17 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B20" s="8" t="n"/>
+        <v>47</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
@@ -13482,15 +13482,15 @@
       <c r="A21" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -13544,11 +13544,11 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
@@ -13560,13 +13560,13 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -13582,7 +13582,7 @@
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -13614,7 +13614,7 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -13624,13 +13624,13 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -13644,31 +13644,31 @@
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -13688,15 +13688,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -13704,15 +13704,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -13752,7 +13752,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -13772,43 +13772,43 @@
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -13822,7 +13822,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -13838,7 +13838,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -13848,15 +13848,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -13864,13 +13864,13 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -13882,13 +13882,13 @@
       <c r="A46" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -13896,7 +13896,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -13960,11 +13960,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -13980,7 +13980,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -14104,11 +14104,11 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -14124,7 +14124,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -14216,15 +14216,15 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -14232,17 +14232,17 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="n"/>
     </row>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -14266,13 +14266,13 @@
       <c r="A70" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B70" s="8" t="n"/>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -14282,13 +14282,13 @@
       <c r="A71" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B71" s="8" t="n"/>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -14302,7 +14302,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -14318,7 +14318,7 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -14334,7 +14334,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -14350,7 +14350,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -14364,13 +14364,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -14382,13 +14382,13 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -14402,25 +14402,25 @@
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -14432,7 +14432,7 @@
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G80" s="8" t="n"/>
@@ -14734,7 +14734,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -14748,31 +14748,31 @@
       </c>
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
-      <c r="H101" s="8" t="n"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -14780,7 +14780,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C102" s="8" t="n"/>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C103" s="8" t="n"/>
@@ -14810,13 +14810,13 @@
       <c r="A104" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B104" s="8" t="n"/>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
@@ -15020,13 +15020,13 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -15036,15 +15036,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>69</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -15054,13 +15054,13 @@
       <c r="A8" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -15074,7 +15074,7 @@
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -15084,13 +15084,13 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -15132,7 +15132,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -15212,15 +15212,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -15230,13 +15230,13 @@
       <c r="A19" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -15244,17 +15244,17 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B20" s="8" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
@@ -15262,15 +15262,15 @@
       <c r="A21" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -15324,11 +15324,11 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
@@ -15340,13 +15340,13 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -15362,7 +15362,7 @@
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -15374,13 +15374,13 @@
       <c r="A28" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -15390,13 +15390,13 @@
       <c r="A29" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -15420,39 +15420,39 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
@@ -15470,13 +15470,13 @@
       <c r="A34" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -15484,15 +15484,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -15504,7 +15504,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -15516,11 +15516,11 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
@@ -15532,7 +15532,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -15548,7 +15548,7 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
@@ -15650,7 +15650,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -15660,15 +15660,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -15676,15 +15676,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B47" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -15740,11 +15740,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -15884,11 +15884,11 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -15996,15 +15996,15 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -16012,17 +16012,17 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="n"/>
     </row>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -16046,13 +16046,13 @@
       <c r="A70" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B70" s="8" t="n"/>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -16062,13 +16062,13 @@
       <c r="A71" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B71" s="8" t="n"/>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -16082,7 +16082,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -16098,7 +16098,7 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -16114,7 +16114,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -16130,7 +16130,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -16144,13 +16144,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -16162,13 +16162,13 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -16182,25 +16182,25 @@
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -16212,7 +16212,7 @@
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G80" s="8" t="n"/>
@@ -16514,7 +16514,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -16528,31 +16528,31 @@
       </c>
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
-      <c r="H101" s="8" t="n"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C102" s="8" t="n"/>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C103" s="8" t="n"/>
@@ -16590,13 +16590,13 @@
       <c r="A104" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B104" s="8" t="n"/>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -748,7 +748,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
       <c r="A28" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -1184,43 +1184,43 @@
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -1374,13 +1374,13 @@
       <c r="A43" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -1388,15 +1388,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B44" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -1500,11 +1500,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -1516,11 +1516,11 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -2882,13 +2882,13 @@
       <c r="A26" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -2896,15 +2896,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -2912,15 +2912,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -2934,7 +2934,7 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -2950,7 +2950,7 @@
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -2960,15 +2960,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -2976,15 +2976,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -2998,7 +2998,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -3008,15 +3008,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -3122,13 +3122,13 @@
       <c r="A41" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -3136,15 +3136,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -3154,13 +3154,13 @@
       <c r="A43" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -3168,11 +3168,11 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
@@ -3184,15 +3184,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C46" s="8" t="n"/>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -4662,13 +4662,13 @@
       <c r="A26" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -4676,15 +4676,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -4694,13 +4694,13 @@
       <c r="A28" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -4708,13 +4708,13 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -4730,7 +4730,7 @@
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -4740,15 +4740,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -4756,15 +4756,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -4778,7 +4778,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -4792,31 +4792,31 @@
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -4916,11 +4916,11 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
@@ -4934,13 +4934,13 @@
       <c r="A43" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -4948,11 +4948,11 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
@@ -4964,15 +4964,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C46" s="8" t="n"/>
@@ -6088,7 +6088,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -6442,13 +6442,13 @@
       <c r="A26" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -6456,15 +6456,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -6472,15 +6472,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B28" s="8" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -6494,7 +6494,7 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -6510,7 +6510,7 @@
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -6520,15 +6520,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -6536,15 +6536,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -6572,31 +6572,31 @@
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -6682,13 +6682,13 @@
       <c r="A41" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -6696,15 +6696,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -6714,13 +6714,13 @@
       <c r="A43" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -6728,11 +6728,11 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
@@ -6744,15 +6744,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C46" s="8" t="n"/>
@@ -8238,13 +8238,13 @@
       <c r="A27" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -8258,7 +8258,7 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -8268,15 +8268,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -8286,13 +8286,13 @@
       <c r="A30" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B30" s="8" t="n"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -8300,13 +8300,13 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -8316,13 +8316,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -8332,15 +8332,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -8478,13 +8478,13 @@
       <c r="A42" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -8498,7 +8498,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -8508,15 +8508,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B44" s="8" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -8574,13 +8574,13 @@
       <c r="A48" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -8588,15 +8588,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -8620,11 +8620,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -9648,7 +9648,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -10018,13 +10018,13 @@
       <c r="A27" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -10038,7 +10038,7 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -10048,15 +10048,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -10066,13 +10066,13 @@
       <c r="A30" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B30" s="8" t="n"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -10080,13 +10080,13 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -10096,13 +10096,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -10112,15 +10112,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -10258,13 +10258,13 @@
       <c r="A42" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -10278,7 +10278,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -10288,15 +10288,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B44" s="8" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -10354,13 +10354,13 @@
       <c r="A48" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -10368,15 +10368,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -10400,11 +10400,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -11798,13 +11798,13 @@
       <c r="A27" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -11818,7 +11818,7 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -11828,15 +11828,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -11846,13 +11846,13 @@
       <c r="A30" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B30" s="8" t="n"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -11860,13 +11860,13 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -11876,13 +11876,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -11892,15 +11892,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -12038,13 +12038,13 @@
       <c r="A42" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -12058,7 +12058,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -12068,15 +12068,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B44" s="8" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -12134,13 +12134,13 @@
       <c r="A48" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -12148,15 +12148,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -12180,11 +12180,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -13208,7 +13208,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -13610,13 +13610,13 @@
       <c r="A29" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B29" s="8" t="n"/>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -13630,7 +13630,7 @@
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -13644,43 +13644,43 @@
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -13834,13 +13834,13 @@
       <c r="A43" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -13848,15 +13848,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B44" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -13960,11 +13960,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -13976,11 +13976,11 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -14988,7 +14988,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -15374,13 +15374,13 @@
       <c r="A28" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -15420,47 +15420,47 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -15614,13 +15614,13 @@
       <c r="A43" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -15634,7 +15634,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -15650,7 +15650,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -15660,15 +15660,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B46" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C47" s="8" t="n"/>
@@ -15740,11 +15740,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -15756,11 +15756,11 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -764,7 +764,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -782,13 +782,13 @@
       <c r="A6" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -796,15 +796,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -828,13 +828,13 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -844,13 +844,13 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -910,13 +910,13 @@
       <c r="A14" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -924,15 +924,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -944,7 +944,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -1006,13 +1006,13 @@
       <c r="A20" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="B20" s="8" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -1020,15 +1020,15 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -1068,13 +1068,13 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1084,15 +1084,15 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -1102,13 +1102,13 @@
       <c r="A26" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -1132,15 +1132,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -1148,11 +1148,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -1166,13 +1166,13 @@
       <c r="A30" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B30" s="8" t="n"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1200,31 +1200,31 @@
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1342,13 +1342,13 @@
       <c r="A41" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -1356,15 +1356,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -1378,7 +1378,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1388,15 +1388,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -1422,13 +1422,13 @@
       <c r="A46" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -2672,15 +2672,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B13" s="8" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -2690,13 +2690,13 @@
       <c r="A14" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
       <c r="A16" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B16" s="8" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -2736,15 +2736,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -2852,39 +2852,39 @@
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -2898,13 +2898,13 @@
       <c r="A27" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -2912,15 +2912,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -2928,15 +2928,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -2992,13 +2992,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -3014,7 +3014,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -3106,13 +3106,13 @@
       <c r="A40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -3120,15 +3120,15 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B41" s="8" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -3152,15 +3152,15 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B43" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -3202,13 +3202,13 @@
       <c r="A46" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -3216,13 +3216,13 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -3238,7 +3238,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -3248,15 +3248,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -3266,13 +3266,13 @@
       <c r="A50" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
@@ -3286,7 +3286,7 @@
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -3296,13 +3296,13 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
       <c r="A16" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B16" s="8" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -4516,15 +4516,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -4644,15 +4644,15 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -4660,11 +4660,11 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -4678,13 +4678,13 @@
       <c r="A27" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -4692,15 +4692,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -4710,13 +4710,13 @@
       <c r="A29" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B29" s="8" t="n"/>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -4724,13 +4724,13 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -4772,13 +4772,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -4794,7 +4794,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -4948,15 +4948,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C46" s="8" t="n"/>
@@ -4996,15 +4996,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B47" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -5018,7 +5018,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -5066,7 +5066,7 @@
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -5076,13 +5076,13 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -6136,11 +6136,11 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -6232,7 +6232,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
       <c r="A16" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B16" s="8" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -6296,15 +6296,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -6424,15 +6424,15 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -6440,11 +6440,11 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -6458,13 +6458,13 @@
       <c r="A27" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -6472,15 +6472,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -6488,15 +6488,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -6536,15 +6536,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -6552,15 +6552,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -6666,13 +6666,13 @@
       <c r="A40" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -6680,15 +6680,15 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B41" s="8" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -6712,15 +6712,15 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="8" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -6762,13 +6762,13 @@
       <c r="A46" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -6776,13 +6776,13 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -6798,7 +6798,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -6808,15 +6808,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -6826,13 +6826,13 @@
       <c r="A50" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
@@ -6846,7 +6846,7 @@
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -6856,13 +6856,13 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -7884,7 +7884,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
       <c r="A17" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B17" s="8" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -8092,15 +8092,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -8188,15 +8188,15 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -8206,13 +8206,13 @@
       <c r="A25" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -8224,43 +8224,43 @@
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -8306,7 +8306,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -8316,13 +8316,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -8332,13 +8332,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -8444,7 +8444,7 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
@@ -8460,13 +8460,13 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -8482,7 +8482,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -8498,7 +8498,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -8508,15 +8508,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -8542,13 +8542,13 @@
       <c r="A46" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -8562,7 +8562,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -8578,7 +8578,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -9858,13 +9858,13 @@
       <c r="A17" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B17" s="8" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -9872,15 +9872,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -9968,15 +9968,15 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -9986,13 +9986,13 @@
       <c r="A25" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -10000,47 +10000,47 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -10086,7 +10086,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -10096,13 +10096,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -10112,13 +10112,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -10224,7 +10224,7 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
@@ -10240,13 +10240,13 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -10262,7 +10262,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -10278,7 +10278,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -10288,15 +10288,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -10322,13 +10322,13 @@
       <c r="A46" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -10342,7 +10342,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -10358,7 +10358,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -11604,7 +11604,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -11638,13 +11638,13 @@
       <c r="A17" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B17" s="8" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -11652,15 +11652,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -11748,15 +11748,15 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -11766,13 +11766,13 @@
       <c r="A25" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -11780,47 +11780,47 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -11866,7 +11866,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -11876,13 +11876,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -11892,13 +11892,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -12004,7 +12004,7 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
@@ -12020,13 +12020,13 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -12042,7 +12042,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -12058,7 +12058,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -12068,15 +12068,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -12102,13 +12102,13 @@
       <c r="A46" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -12122,7 +12122,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -12138,7 +12138,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -13224,7 +13224,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -13242,13 +13242,13 @@
       <c r="A6" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -13256,15 +13256,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -13304,7 +13304,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -13528,13 +13528,13 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -13544,15 +13544,15 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -13562,13 +13562,13 @@
       <c r="A26" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -13592,15 +13592,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -13626,13 +13626,13 @@
       <c r="A30" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B30" s="8" t="n"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -13640,13 +13640,13 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -13660,31 +13660,31 @@
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -13786,13 +13786,13 @@
       <c r="A40" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -13800,15 +13800,15 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B41" s="8" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -13816,13 +13816,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -13838,7 +13838,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -13848,15 +13848,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
@@ -13882,13 +13882,13 @@
       <c r="A46" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -13896,7 +13896,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -15004,7 +15004,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -15022,13 +15022,13 @@
       <c r="A6" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -15036,15 +15036,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>69</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -15084,7 +15084,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -15150,13 +15150,13 @@
       <c r="A14" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -15164,15 +15164,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -15230,13 +15230,13 @@
       <c r="A19" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B19" s="8" t="n"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -15248,29 +15248,29 @@
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
@@ -15308,13 +15308,13 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -15324,15 +15324,15 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -15342,13 +15342,13 @@
       <c r="A26" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -15372,15 +15372,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -15388,11 +15388,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -15406,13 +15406,13 @@
       <c r="A30" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B30" s="8" t="n"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -15426,7 +15426,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -15436,35 +15436,35 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -15582,13 +15582,13 @@
       <c r="A41" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -15596,15 +15596,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -15634,7 +15634,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -15644,15 +15644,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C46" s="8" t="n"/>
@@ -15676,15 +15676,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -1020,7 +1020,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -1052,33 +1052,33 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -1086,27 +1086,27 @@
       <c r="A25" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1120,13 +1120,13 @@
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
     </row>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
@@ -2800,17 +2800,17 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -2820,45 +2820,45 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
@@ -3488,31 +3488,31 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -3524,13 +3524,13 @@
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
     </row>
@@ -3542,13 +3542,13 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -4484,35 +4484,35 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -4564,17 +4564,17 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -4584,45 +4584,45 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
@@ -5252,19 +5252,19 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -5318,13 +5318,13 @@
       <c r="A69" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B69" s="8" t="n"/>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -5336,13 +5336,13 @@
       </c>
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="n"/>
     </row>
@@ -5354,13 +5354,13 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -6248,35 +6248,35 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -6328,17 +6328,17 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -6348,45 +6348,45 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
@@ -8076,7 +8076,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -8092,7 +8092,7 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
@@ -8124,31 +8124,31 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -8160,13 +8160,13 @@
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -8940,19 +8940,19 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="n"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -8962,13 +8962,13 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -9840,7 +9840,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -9856,7 +9856,7 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
@@ -9888,31 +9888,31 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -9924,13 +9924,13 @@
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -10704,19 +10704,19 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="n"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C76" s="8" t="n"/>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C77" s="8" t="n"/>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -10770,13 +10770,13 @@
       <c r="A79" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B79" s="8" t="n"/>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -10790,7 +10790,7 @@
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -10804,13 +10804,13 @@
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
     </row>
@@ -10822,13 +10822,13 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -11604,7 +11604,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -11620,7 +11620,7 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
@@ -11652,31 +11652,31 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -11688,13 +11688,13 @@
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -13400,47 +13400,47 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -13448,15 +13448,15 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -13468,13 +13468,13 @@
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
     </row>
@@ -14376,33 +14376,33 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B85" s="8" t="n"/>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
     </row>
@@ -14414,13 +14414,13 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -15132,7 +15132,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -15164,33 +15164,33 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -15198,27 +15198,27 @@
       <c r="A25" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -15232,13 +15232,13 @@
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
     </row>
@@ -16124,31 +16124,31 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="8" t="n"/>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
@@ -16160,13 +16160,13 @@
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
     </row>
@@ -16178,13 +16178,13 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -764,7 +764,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -782,13 +782,13 @@
       <c r="A6" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" s="8" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -796,15 +796,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -812,7 +812,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
@@ -860,7 +860,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -908,7 +908,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -974,13 +974,13 @@
       <c r="A18" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -988,15 +988,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -1116,15 +1116,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B27" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -1132,15 +1132,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -1164,11 +1164,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -1212,13 +1212,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1234,7 +1234,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1250,7 +1250,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1276,11 +1276,11 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
@@ -1310,13 +1310,13 @@
       <c r="A39" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -1326,13 +1326,13 @@
       <c r="A40" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -1346,7 +1346,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1356,15 +1356,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -1374,13 +1374,13 @@
       <c r="A43" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B43" s="8" t="n"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -1390,13 +1390,13 @@
       <c r="A44" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B44" s="8" t="n"/>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -1404,15 +1404,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -1484,33 +1484,33 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -1566,13 +1566,13 @@
       <c r="A55" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -1580,15 +1580,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -1662,13 +1662,13 @@
       <c r="A61" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -1676,15 +1676,15 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B62" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C63" s="8" t="n"/>
@@ -1772,19 +1772,19 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B70" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -1822,13 +1822,13 @@
       <c r="A71" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -2002,13 +2002,13 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -2022,37 +2022,37 @@
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" s="8" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -2064,13 +2064,13 @@
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
     </row>
@@ -2358,7 +2358,7 @@
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -2576,11 +2576,11 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
@@ -2642,13 +2642,13 @@
       <c r="A12" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -2656,15 +2656,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B13" s="8" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -2804,29 +2804,29 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
@@ -2834,13 +2834,13 @@
       <c r="A24" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
@@ -2912,11 +2912,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -2928,15 +2928,15 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" s="8" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -2960,15 +2960,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -3106,13 +3106,13 @@
       <c r="A41" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -3120,15 +3120,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C48" s="8" t="n"/>
@@ -3234,13 +3234,13 @@
       <c r="A49" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -3254,7 +3254,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -3268,31 +3268,31 @@
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B52" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -3318,13 +3318,13 @@
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -3392,17 +3392,17 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B59" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -3442,13 +3442,13 @@
       <c r="A62" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -3462,7 +3462,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -3476,15 +3476,15 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -3498,7 +3498,7 @@
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -3514,37 +3514,37 @@
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -3558,7 +3558,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -3572,13 +3572,13 @@
       </c>
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="n"/>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="n"/>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C72" s="8" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C73" s="8" t="n"/>
@@ -3632,11 +3632,11 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -3648,17 +3648,17 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="n"/>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
     </row>
@@ -3666,13 +3666,13 @@
       <c r="A76" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -3686,7 +3686,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -3700,13 +3700,13 @@
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
     </row>
@@ -3898,7 +3898,7 @@
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       <c r="G92" s="8" t="n"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -3970,13 +3970,13 @@
       <c r="A95" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B95" s="8" t="n"/>
       <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n"/>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
@@ -3990,7 +3990,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -4006,7 +4006,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -4020,31 +4020,31 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B99" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -4070,7 +4070,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -4086,7 +4086,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -4102,7 +4102,7 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -4112,13 +4112,13 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B104" s="8" t="n"/>
       <c r="C104" s="8" t="n"/>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -4292,7 +4292,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -4308,11 +4308,11 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -4324,11 +4324,11 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -4372,15 +4372,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -4404,13 +4404,13 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -4420,15 +4420,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B13" s="8" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -4552,43 +4552,43 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B23" s="8" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
@@ -4676,11 +4676,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -4692,15 +4692,15 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C32" s="8" t="n"/>
@@ -4740,15 +4740,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -4870,13 +4870,13 @@
       <c r="A41" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -4884,15 +4884,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C48" s="8" t="n"/>
@@ -4998,13 +4998,13 @@
       <c r="A49" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -5018,7 +5018,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -5032,31 +5032,31 @@
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B52" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -5082,13 +5082,13 @@
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -5156,17 +5156,17 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B59" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -5206,13 +5206,13 @@
       <c r="A62" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -5226,7 +5226,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -5240,15 +5240,15 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -5262,7 +5262,7 @@
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -5278,25 +5278,25 @@
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -5350,13 +5350,13 @@
       <c r="A71" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -5370,7 +5370,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -5384,29 +5384,29 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -5414,13 +5414,13 @@
       <c r="A75" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -5430,13 +5430,13 @@
       <c r="A76" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -5448,27 +5448,27 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -5630,7 +5630,7 @@
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
       <c r="G92" s="8" t="n"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -5734,13 +5734,13 @@
       <c r="A95" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B95" s="8" t="n"/>
       <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n"/>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
@@ -5754,7 +5754,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -5770,7 +5770,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -5784,31 +5784,31 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B99" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -5834,7 +5834,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -5850,7 +5850,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -5866,7 +5866,7 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -5876,13 +5876,13 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B104" s="8" t="n"/>
       <c r="C104" s="8" t="n"/>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -6104,15 +6104,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -6138,13 +6138,13 @@
       <c r="A10" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="B10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -6158,7 +6158,7 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -6170,13 +6170,13 @@
       <c r="A12" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -6184,15 +6184,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B13" s="8" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -6316,43 +6316,43 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B23" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -6392,15 +6392,15 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -6408,15 +6408,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -6440,15 +6440,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -6456,11 +6456,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -6488,15 +6488,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -6634,13 +6634,13 @@
       <c r="A41" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -6648,15 +6648,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -6728,7 +6728,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C48" s="8" t="n"/>
@@ -6762,13 +6762,13 @@
       <c r="A49" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -6782,7 +6782,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -6792,15 +6792,15 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -6808,19 +6808,19 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -6828,45 +6828,45 @@
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -6920,17 +6920,17 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -6970,13 +6970,13 @@
       <c r="A62" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -6990,7 +6990,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -7006,7 +7006,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -7020,13 +7020,13 @@
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
@@ -7160,17 +7160,17 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C75" s="8" t="n"/>
@@ -7194,13 +7194,13 @@
       <c r="A76" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -7214,7 +7214,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -7228,13 +7228,13 @@
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
     </row>
@@ -7426,7 +7426,7 @@
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       <c r="G94" s="8" t="n"/>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C95" s="8" t="n"/>
@@ -7514,13 +7514,13 @@
       <c r="A96" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
@@ -7534,7 +7534,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -7550,7 +7550,7 @@
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -7564,31 +7564,31 @@
       </c>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="8" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C100" s="8" t="n"/>
       <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -7598,7 +7598,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -7614,7 +7614,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -7630,7 +7630,7 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -7640,15 +7640,15 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B104" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C105" s="8" t="n"/>
@@ -7674,13 +7674,13 @@
       <c r="A106" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B106" s="8" t="n"/>
       <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E106" s="8" t="n"/>
       <c r="F106" s="8" t="n"/>
       <c r="G106" s="8" t="n"/>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -7854,13 +7854,13 @@
       <c r="A7" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -7874,7 +7874,7 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -7884,15 +7884,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -7964,7 +7964,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -8014,13 +8014,13 @@
       <c r="A17" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -8028,15 +8028,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -8080,29 +8080,29 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -8158,13 +8158,13 @@
       <c r="A26" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -8172,13 +8172,13 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -8188,11 +8188,11 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -8206,13 +8206,13 @@
       <c r="A29" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -8236,7 +8236,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
@@ -8270,13 +8270,13 @@
       <c r="A33" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -8290,7 +8290,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -8300,15 +8300,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B35" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -8316,15 +8316,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B36" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -8334,13 +8334,13 @@
       <c r="A37" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -8350,13 +8350,13 @@
       <c r="A38" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -8368,31 +8368,31 @@
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
@@ -8476,15 +8476,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -8494,13 +8494,13 @@
       <c r="A47" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B47" s="8" t="n"/>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -8542,15 +8542,15 @@
       <c r="A50" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -8558,13 +8558,13 @@
       <c r="A51" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B51" s="8" t="n"/>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -8576,13 +8576,13 @@
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
     </row>
@@ -8652,19 +8652,19 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -8700,19 +8700,19 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -8812,17 +8812,17 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -8862,13 +8862,13 @@
       <c r="A70" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -8882,7 +8882,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -8898,7 +8898,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -8912,15 +8912,15 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -8934,7 +8934,7 @@
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -8950,53 +8950,53 @@
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B78" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -9084,17 +9084,17 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
     </row>
@@ -9102,13 +9102,13 @@
       <c r="A85" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B85" s="8" t="n"/>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -9122,7 +9122,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -9132,17 +9132,17 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B87" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C88" s="8" t="n"/>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -9182,13 +9182,13 @@
       <c r="A90" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
@@ -9202,7 +9202,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -9218,7 +9218,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -9234,7 +9234,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -9250,7 +9250,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -9266,7 +9266,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -9282,7 +9282,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -9318,7 +9318,7 @@
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -9634,13 +9634,13 @@
       <c r="A8" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -9648,15 +9648,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -9778,13 +9778,13 @@
       <c r="A17" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -9792,15 +9792,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -9844,29 +9844,29 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -9922,13 +9922,13 @@
       <c r="A26" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -9936,13 +9936,13 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -9952,11 +9952,11 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -9970,13 +9970,13 @@
       <c r="A29" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -10000,7 +10000,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
@@ -10034,13 +10034,13 @@
       <c r="A33" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -10054,7 +10054,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -10064,15 +10064,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B35" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -10080,15 +10080,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B36" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -10096,15 +10096,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -10114,13 +10114,13 @@
       <c r="A38" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -10132,31 +10132,31 @@
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
@@ -10240,15 +10240,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -10258,13 +10258,13 @@
       <c r="A47" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B47" s="8" t="n"/>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -10306,15 +10306,15 @@
       <c r="A50" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -10322,13 +10322,13 @@
       <c r="A51" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B51" s="8" t="n"/>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -10340,13 +10340,13 @@
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
     </row>
@@ -10416,19 +10416,19 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -10464,19 +10464,19 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -10576,17 +10576,17 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -10626,13 +10626,13 @@
       <c r="A70" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -10646,7 +10646,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -10662,7 +10662,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -10676,15 +10676,15 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -10698,7 +10698,7 @@
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -10714,25 +10714,25 @@
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B76" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C77" s="8" t="n"/>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -10786,13 +10786,13 @@
       <c r="A80" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B80" s="8" t="n"/>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
@@ -10806,7 +10806,7 @@
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -10822,7 +10822,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -10836,29 +10836,29 @@
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
     </row>
@@ -10866,13 +10866,13 @@
       <c r="A85" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="8" t="n"/>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -10886,7 +10886,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -10896,17 +10896,17 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B87" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C88" s="8" t="n"/>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -10946,13 +10946,13 @@
       <c r="A90" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
@@ -10966,7 +10966,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -10982,7 +10982,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -10998,7 +10998,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -11014,7 +11014,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -11030,7 +11030,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -11046,7 +11046,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -11082,7 +11082,7 @@
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -11398,13 +11398,13 @@
       <c r="A8" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -11412,15 +11412,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -11542,13 +11542,13 @@
       <c r="A17" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -11556,15 +11556,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -11608,29 +11608,29 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -11686,13 +11686,13 @@
       <c r="A26" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -11700,13 +11700,13 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -11716,11 +11716,11 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -11734,13 +11734,13 @@
       <c r="A29" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -11764,7 +11764,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
@@ -11798,13 +11798,13 @@
       <c r="A33" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -11818,7 +11818,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -11828,15 +11828,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B35" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -11844,15 +11844,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B36" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -11860,15 +11860,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -11878,13 +11878,13 @@
       <c r="A38" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -11896,31 +11896,31 @@
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
@@ -12004,15 +12004,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -12022,13 +12022,13 @@
       <c r="A47" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B47" s="8" t="n"/>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -12180,19 +12180,19 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -12228,19 +12228,19 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -12442,13 +12442,13 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -12462,39 +12462,39 @@
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -12504,31 +12504,31 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B78" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -12612,17 +12612,17 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
     </row>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C85" s="8" t="n"/>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C86" s="8" t="n"/>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C87" s="8" t="n"/>
@@ -12678,13 +12678,13 @@
       <c r="A88" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B88" s="8" t="n"/>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
@@ -12698,7 +12698,7 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -12808,13 +12808,13 @@
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
     </row>
@@ -12846,7 +12846,7 @@
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -12894,7 +12894,7 @@
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -12910,7 +12910,7 @@
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -13112,7 +13112,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -13130,13 +13130,13 @@
       <c r="A6" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B6" s="8" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -13144,15 +13144,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -13160,7 +13160,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
@@ -13208,7 +13208,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -13272,11 +13272,11 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -13288,11 +13288,11 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -13464,15 +13464,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B27" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -13480,15 +13480,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -13512,7 +13512,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -13560,13 +13560,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -13582,7 +13582,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -13598,7 +13598,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -13624,11 +13624,11 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
@@ -13658,13 +13658,13 @@
       <c r="A39" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -13674,13 +13674,13 @@
       <c r="A40" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -13694,7 +13694,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -13704,15 +13704,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -13722,13 +13722,13 @@
       <c r="A43" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B43" s="8" t="n"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -13738,13 +13738,13 @@
       <c r="A44" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B44" s="8" t="n"/>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -13752,15 +13752,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -13834,15 +13834,15 @@
       <c r="A50" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -13850,15 +13850,15 @@
       <c r="A51" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B51" s="8" t="n"/>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -13914,13 +13914,13 @@
       <c r="A55" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -13928,15 +13928,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -14026,13 +14026,13 @@
       <c r="A62" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -14046,7 +14046,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -14062,7 +14062,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -14072,15 +14072,15 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B65" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -14120,19 +14120,19 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -14140,27 +14140,27 @@
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -14170,13 +14170,13 @@
       <c r="A71" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -14264,17 +14264,17 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B77" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -14330,13 +14330,13 @@
       <c r="A81" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -14350,7 +14350,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -14364,15 +14364,15 @@
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -14386,7 +14386,7 @@
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -14402,39 +14402,39 @@
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B86" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
@@ -14488,17 +14488,17 @@
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
-      <c r="F91" s="8" t="n"/>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
     </row>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C92" s="8" t="n"/>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C93" s="8" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C95" s="8" t="n"/>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C96" s="8" t="n"/>
@@ -14586,13 +14586,13 @@
       <c r="A97" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B97" s="8" t="n"/>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
@@ -14606,7 +14606,7 @@
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -14622,7 +14622,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -14638,7 +14638,7 @@
       <c r="C100" s="8" t="n"/>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -14654,7 +14654,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -14668,13 +14668,13 @@
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
     </row>
@@ -14706,7 +14706,7 @@
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -14722,7 +14722,7 @@
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14876,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -14894,13 +14894,13 @@
       <c r="A6" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B6" s="8" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -14908,15 +14908,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -14924,7 +14924,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
@@ -14958,13 +14958,13 @@
       <c r="A10" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -14972,15 +14972,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B11" s="8" t="n"/>
+        <v>59</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -15004,7 +15004,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -15020,7 +15020,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -15036,11 +15036,11 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -15052,11 +15052,11 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -15086,13 +15086,13 @@
       <c r="A18" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -15100,15 +15100,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -15120,29 +15120,29 @@
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
@@ -15228,15 +15228,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B27" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -15244,15 +15244,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -15324,13 +15324,13 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -15346,7 +15346,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -15362,7 +15362,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -15388,11 +15388,11 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
@@ -15422,13 +15422,13 @@
       <c r="A39" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -15438,13 +15438,13 @@
       <c r="A40" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -15458,7 +15458,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -15468,15 +15468,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -15486,13 +15486,13 @@
       <c r="A43" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B43" s="8" t="n"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -15502,13 +15502,13 @@
       <c r="A44" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B44" s="8" t="n"/>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -15516,15 +15516,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -15598,15 +15598,15 @@
       <c r="A50" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -15614,15 +15614,15 @@
       <c r="A51" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B51" s="8" t="n"/>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -15678,13 +15678,13 @@
       <c r="A55" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -15692,15 +15692,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -15806,13 +15806,13 @@
       <c r="A63" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -15826,7 +15826,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -15842,7 +15842,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -15852,15 +15852,15 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -15868,19 +15868,19 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -15888,15 +15888,15 @@
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -15936,13 +15936,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -15956,7 +15956,7 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G72" s="8" t="n"/>
@@ -15964,33 +15964,33 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -16000,7 +16000,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C75" s="8" t="n"/>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C76" s="8" t="n"/>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C77" s="8" t="n"/>
@@ -16046,13 +16046,13 @@
       <c r="A78" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -16066,7 +16066,7 @@
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -16082,7 +16082,7 @@
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -16098,7 +16098,7 @@
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -16112,15 +16112,15 @@
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -16134,7 +16134,7 @@
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -16150,37 +16150,37 @@
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
@@ -16192,13 +16192,13 @@
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
@@ -16252,17 +16252,17 @@
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
-      <c r="F91" s="8" t="n"/>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
     </row>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C92" s="8" t="n"/>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C93" s="8" t="n"/>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C95" s="8" t="n"/>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C96" s="8" t="n"/>
@@ -16350,13 +16350,13 @@
       <c r="A97" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B97" s="8" t="n"/>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
@@ -16370,7 +16370,7 @@
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -16386,7 +16386,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -16402,7 +16402,7 @@
       <c r="C100" s="8" t="n"/>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -16418,7 +16418,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -16432,13 +16432,13 @@
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
     </row>
@@ -16470,7 +16470,7 @@
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -16486,7 +16486,7 @@
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -780,15 +780,15 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -796,13 +796,13 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -812,15 +812,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>69</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -828,7 +828,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -844,7 +844,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -860,7 +860,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -926,13 +926,13 @@
       <c r="A15" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -940,11 +940,11 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -956,15 +956,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -972,15 +972,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -988,15 +988,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -1004,23 +1004,23 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B20" s="8" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -1036,17 +1036,17 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -1054,33 +1054,33 @@
       <c r="A23" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1102,13 +1102,13 @@
       <c r="A26" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -1116,15 +1116,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -1218,7 +1218,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1228,13 +1228,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1244,13 +1244,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1260,15 +1260,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B36" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -1278,13 +1278,13 @@
       <c r="A37" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -1310,13 +1310,13 @@
       <c r="A39" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -1330,7 +1330,7 @@
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1346,7 +1346,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
@@ -1390,13 +1390,13 @@
       <c r="A44" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -1410,7 +1410,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1422,43 +1422,43 @@
       <c r="A46" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B47" s="8" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1474,7 +1474,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
@@ -1548,13 +1548,13 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1566,13 +1566,13 @@
       <c r="A55" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -1580,15 +1580,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -1676,15 +1676,15 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C63" s="8" t="n"/>
@@ -1710,13 +1710,13 @@
       <c r="A64" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B64" s="8" t="n"/>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -1730,7 +1730,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1746,7 +1746,7 @@
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1774,13 +1774,13 @@
       <c r="A68" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B68" s="8" t="n"/>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -1792,27 +1792,27 @@
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -1820,19 +1820,19 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="n"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -2358,7 +2358,7 @@
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -2544,11 +2544,11 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -2560,11 +2560,11 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -2576,15 +2576,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -2592,15 +2592,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -2608,15 +2608,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -2624,15 +2624,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B11" s="8" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -2752,15 +2752,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -2768,13 +2768,13 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -2784,15 +2784,15 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -2802,13 +2802,13 @@
       <c r="A22" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B22" s="8" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -2820,29 +2820,29 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -2864,11 +2864,11 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -2912,11 +2912,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -3030,7 +3030,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -3040,13 +3040,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -3056,15 +3056,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -3072,11 +3072,11 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -3104,15 +3104,15 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -3126,7 +3126,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -3136,15 +3136,15 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -3158,7 +3158,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -3168,15 +3168,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
@@ -3216,15 +3216,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -3234,13 +3234,13 @@
       <c r="A49" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -3254,7 +3254,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -3298,13 +3298,13 @@
       <c r="A53" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -3316,31 +3316,31 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -3392,15 +3392,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -3442,13 +3442,13 @@
       <c r="A62" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B62" s="8" t="n"/>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -3462,7 +3462,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -3476,15 +3476,15 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -3494,13 +3494,13 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -3514,53 +3514,53 @@
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="n"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B69" s="8" t="n"/>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -3570,25 +3570,25 @@
       <c r="A70" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B70" s="8" t="n"/>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -3600,11 +3600,11 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C72" s="8" t="n"/>
@@ -3616,17 +3616,17 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -3652,27 +3652,27 @@
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -3680,13 +3680,13 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -3698,13 +3698,13 @@
       <c r="A78" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B78" s="8" t="n"/>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -3712,7 +3712,7 @@
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -3776,13 +3776,13 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -3792,13 +3792,13 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -3808,13 +3808,13 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -3824,13 +3824,13 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -3840,49 +3840,49 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B89" s="8" t="n"/>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
     </row>
@@ -3892,27 +3892,27 @@
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="8" t="n"/>
@@ -3930,13 +3930,13 @@
       <c r="G92" s="8" t="n"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
@@ -3946,7 +3946,7 @@
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -4086,7 +4086,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -4102,7 +4102,7 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -4112,13 +4112,13 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B104" s="8" t="n"/>
       <c r="C104" s="8" t="n"/>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -4324,11 +4324,11 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -4340,15 +4340,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -4356,7 +4356,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -4374,13 +4374,13 @@
       <c r="A10" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -4390,13 +4390,13 @@
       <c r="A11" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -4406,13 +4406,13 @@
       <c r="A12" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B12" s="8" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -4516,15 +4516,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -4532,13 +4532,13 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -4548,13 +4548,13 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -4566,29 +4566,29 @@
       <c r="A22" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B22" s="8" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -4596,17 +4596,17 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -4614,37 +4614,37 @@
       <c r="A25" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -4676,11 +4676,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -4724,15 +4724,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -4742,13 +4742,13 @@
       <c r="A33" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="8" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
@@ -4794,7 +4794,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -4804,13 +4804,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -4820,15 +4820,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -4838,13 +4838,13 @@
       <c r="A39" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -4854,13 +4854,13 @@
       <c r="A40" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -4868,15 +4868,15 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -4890,7 +4890,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -4900,15 +4900,15 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -4922,7 +4922,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -4932,15 +4932,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
@@ -4980,15 +4980,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -4998,13 +4998,13 @@
       <c r="A49" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -5018,7 +5018,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -5062,13 +5062,13 @@
       <c r="A53" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -5080,31 +5080,31 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -5156,7 +5156,7 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
@@ -5220,7 +5220,7 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
@@ -5252,7 +5252,7 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
@@ -5272,47 +5272,47 @@
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="n"/>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -5350,13 +5350,13 @@
       <c r="A71" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B71" s="8" t="n"/>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -5366,13 +5366,13 @@
       <c r="A72" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B72" s="8" t="n"/>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -5388,7 +5388,7 @@
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G73" s="8" t="n"/>
@@ -5396,17 +5396,17 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -5414,13 +5414,13 @@
       <c r="A75" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -5430,13 +5430,13 @@
       <c r="A76" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -5450,7 +5450,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -5460,15 +5460,15 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B78" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -5530,7 +5530,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -5546,7 +5546,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -5562,7 +5562,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -5594,7 +5594,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -5608,13 +5608,13 @@
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
@@ -5624,59 +5624,59 @@
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="n"/>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B91" s="8" t="n"/>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -5694,7 +5694,7 @@
       <c r="G92" s="8" t="n"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -5850,7 +5850,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -5866,7 +5866,7 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -5876,13 +5876,13 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B104" s="8" t="n"/>
       <c r="C104" s="8" t="n"/>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -6072,11 +6072,11 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -6088,11 +6088,11 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
@@ -6120,15 +6120,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -6136,11 +6136,11 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
@@ -6152,15 +6152,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" s="8" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -6280,15 +6280,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -6296,13 +6296,13 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -6312,13 +6312,13 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -6330,29 +6330,29 @@
       <c r="A22" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B22" s="8" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -6360,17 +6360,17 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -6392,11 +6392,11 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -6440,11 +6440,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
@@ -6558,7 +6558,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -6568,13 +6568,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -6584,15 +6584,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -6600,11 +6600,11 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -6632,15 +6632,15 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -6654,7 +6654,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -6680,15 +6680,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -6698,13 +6698,13 @@
       <c r="A45" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B45" s="8" t="n"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -6728,7 +6728,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -6744,15 +6744,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -6762,13 +6762,13 @@
       <c r="A49" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -6782,7 +6782,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -6792,17 +6792,17 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -6810,13 +6810,13 @@
       <c r="A52" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="8" t="n"/>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -6826,15 +6826,15 @@
       <c r="A53" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
     </row>
@@ -6844,31 +6844,31 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -6920,15 +6920,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -6970,13 +6970,13 @@
       <c r="A62" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="8" t="n"/>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -6986,13 +6986,13 @@
       <c r="A63" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -7006,7 +7006,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -7020,13 +7020,13 @@
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
@@ -7038,13 +7038,13 @@
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="n"/>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -7058,7 +7058,7 @@
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
@@ -7074,25 +7074,25 @@
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -7426,7 +7426,7 @@
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -7450,13 +7450,13 @@
       <c r="A92" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="8" t="n"/>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="8" t="n"/>
@@ -7468,15 +7468,15 @@
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -7484,75 +7484,75 @@
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E94" s="8" t="n"/>
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B95" s="8" t="n"/>
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
-      <c r="H95" s="8" t="n"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="n"/>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B98" s="8" t="n"/>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
@@ -7564,27 +7564,27 @@
       </c>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="n"/>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
@@ -7598,7 +7598,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -7614,7 +7614,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -7630,7 +7630,7 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -7640,15 +7640,15 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B104" s="8" t="n"/>
       <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="n"/>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C105" s="8" t="n"/>
@@ -7674,13 +7674,13 @@
       <c r="A106" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="8" t="n"/>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
       <c r="F106" s="8" t="n"/>
       <c r="G106" s="8" t="n"/>
@@ -7838,13 +7838,13 @@
       <c r="A6" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -7852,7 +7852,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
@@ -7868,15 +7868,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -7884,7 +7884,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -7966,13 +7966,13 @@
       <c r="A14" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -7980,15 +7980,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>47</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -7996,11 +7996,11 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -8044,15 +8044,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -8060,35 +8060,35 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -8096,39 +8096,39 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -8156,11 +8156,11 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -8188,7 +8188,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
@@ -8268,15 +8268,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -8300,7 +8300,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
@@ -8316,15 +8316,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -8332,15 +8332,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B37" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -8350,13 +8350,13 @@
       <c r="A38" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -8364,13 +8364,13 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -8380,35 +8380,35 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -8508,13 +8508,13 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -8530,7 +8530,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -8636,15 +8636,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -8670,13 +8670,13 @@
       <c r="A58" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -8690,7 +8690,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -9132,15 +9132,15 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C88" s="8" t="n"/>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -9182,13 +9182,13 @@
       <c r="A90" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B90" s="8" t="n"/>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
@@ -9202,7 +9202,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -9218,7 +9218,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -9234,7 +9234,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -9250,7 +9250,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -9266,7 +9266,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -9282,7 +9282,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -9318,7 +9318,7 @@
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -9602,13 +9602,13 @@
       <c r="A6" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -9616,7 +9616,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
@@ -9632,15 +9632,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>62</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -9648,7 +9648,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -9680,7 +9680,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -9760,11 +9760,11 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -9776,7 +9776,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -9808,15 +9808,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -9824,35 +9824,35 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -9860,39 +9860,39 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -9906,37 +9906,37 @@
       <c r="A25" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
@@ -10034,13 +10034,13 @@
       <c r="A33" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="8" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -10082,13 +10082,13 @@
       <c r="A36" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -10096,15 +10096,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B37" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -10114,13 +10114,13 @@
       <c r="A38" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -10128,13 +10128,13 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -10144,39 +10144,39 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
@@ -10208,7 +10208,7 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
@@ -10224,7 +10224,7 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
@@ -10272,13 +10272,13 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -10294,7 +10294,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -10400,15 +10400,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -10434,13 +10434,13 @@
       <c r="A58" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -10454,7 +10454,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -10676,15 +10676,15 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -10694,13 +10694,13 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -10714,41 +10714,41 @@
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="n"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -10786,13 +10786,13 @@
       <c r="A80" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B80" s="8" t="n"/>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
@@ -10802,13 +10802,13 @@
       <c r="A81" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B81" s="8" t="n"/>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -10822,7 +10822,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -10836,13 +10836,13 @@
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
     </row>
@@ -10896,15 +10896,15 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C88" s="8" t="n"/>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -10946,13 +10946,13 @@
       <c r="A90" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B90" s="8" t="n"/>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
@@ -10966,7 +10966,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -10982,7 +10982,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -10998,7 +10998,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -11014,7 +11014,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -11030,7 +11030,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -11046,7 +11046,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -11082,7 +11082,7 @@
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -11366,13 +11366,13 @@
       <c r="A6" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -11380,7 +11380,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
@@ -11396,15 +11396,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -11412,7 +11412,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -11492,15 +11492,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -11508,15 +11508,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -11524,11 +11524,11 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -11540,7 +11540,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -11556,7 +11556,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -11572,15 +11572,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -11588,75 +11588,75 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -11684,11 +11684,11 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -11798,13 +11798,13 @@
       <c r="A33" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="8" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -11846,13 +11846,13 @@
       <c r="A36" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -11860,15 +11860,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B37" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -11878,13 +11878,13 @@
       <c r="A38" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -11892,13 +11892,13 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -11908,35 +11908,35 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -12004,7 +12004,7 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
@@ -12020,7 +12020,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
@@ -12036,13 +12036,13 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -12052,13 +12052,13 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -12068,17 +12068,17 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -12086,13 +12086,13 @@
       <c r="A51" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="8" t="n"/>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -12104,13 +12104,13 @@
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
     </row>
@@ -12164,15 +12164,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -12198,13 +12198,13 @@
       <c r="A58" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -12218,7 +12218,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -12264,13 +12264,13 @@
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
@@ -12280,27 +12280,27 @@
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -12308,33 +12308,33 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="n"/>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
     </row>
@@ -12342,13 +12342,13 @@
       <c r="A67" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B67" s="8" t="n"/>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -12358,13 +12358,13 @@
       <c r="A68" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B68" s="8" t="n"/>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -12374,13 +12374,13 @@
       <c r="A69" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B69" s="8" t="n"/>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -12714,7 +12714,7 @@
       <c r="C90" s="8" t="n"/>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -12730,7 +12730,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -12746,7 +12746,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -12762,7 +12762,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -12778,7 +12778,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -12794,7 +12794,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -12810,7 +12810,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -12846,7 +12846,7 @@
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -12894,7 +12894,7 @@
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -12910,7 +12910,7 @@
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13096,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -13128,15 +13128,15 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -13150,7 +13150,7 @@
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -13160,15 +13160,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -13192,7 +13192,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -13208,7 +13208,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -13274,13 +13274,13 @@
       <c r="A15" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -13288,7 +13288,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -13304,15 +13304,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -13322,13 +13322,13 @@
       <c r="A18" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B18" s="8" t="n"/>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -13336,15 +13336,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -13354,21 +13354,21 @@
       <c r="A20" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B20" s="8" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -13384,17 +13384,17 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -13402,47 +13402,47 @@
       <c r="A23" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
@@ -13450,13 +13450,13 @@
       <c r="A26" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -13464,15 +13464,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -13496,7 +13496,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
@@ -13530,13 +13530,13 @@
       <c r="A31" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B31" s="8" t="n"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -13544,15 +13544,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -13566,7 +13566,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -13576,13 +13576,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -13592,13 +13592,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -13610,13 +13610,13 @@
       <c r="A36" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -13624,15 +13624,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -13640,7 +13640,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -13658,13 +13658,13 @@
       <c r="A39" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -13678,7 +13678,7 @@
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -13694,7 +13694,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
@@ -13738,13 +13738,13 @@
       <c r="A44" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -13758,7 +13758,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -13770,13 +13770,13 @@
       <c r="A46" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -13800,15 +13800,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B48" s="8" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -13816,13 +13816,13 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -13864,7 +13864,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
@@ -13896,13 +13896,13 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -13914,13 +13914,13 @@
       <c r="A55" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -13928,15 +13928,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -14122,13 +14122,13 @@
       <c r="A68" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="8" t="n"/>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -14140,27 +14140,27 @@
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -14168,19 +14168,19 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="n"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -14706,7 +14706,7 @@
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -14722,7 +14722,7 @@
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -14892,15 +14892,15 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -14908,13 +14908,13 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -14924,15 +14924,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -14940,7 +14940,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -14956,7 +14956,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -14972,7 +14972,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -15038,13 +15038,13 @@
       <c r="A15" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -15052,7 +15052,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -15068,15 +15068,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -15084,15 +15084,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -15100,15 +15100,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -15116,15 +15116,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B20" s="8" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -15132,7 +15132,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -15148,15 +15148,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -15166,33 +15166,33 @@
       <c r="A23" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -15214,13 +15214,13 @@
       <c r="A26" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -15228,15 +15228,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -15244,7 +15244,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -15260,7 +15260,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
@@ -15330,7 +15330,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -15340,13 +15340,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -15356,13 +15356,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -15372,15 +15372,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B36" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -15390,13 +15390,13 @@
       <c r="A37" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -15404,7 +15404,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -15420,15 +15420,15 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B39" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -15436,7 +15436,7 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
@@ -15454,13 +15454,13 @@
       <c r="A41" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -15468,15 +15468,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -15484,15 +15484,15 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -15532,31 +15532,31 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B46" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -15564,29 +15564,29 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -15628,7 +15628,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
@@ -15660,13 +15660,13 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -15678,13 +15678,13 @@
       <c r="A55" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -15692,15 +15692,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -15806,13 +15806,13 @@
       <c r="A63" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -15826,7 +15826,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -15842,7 +15842,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -15852,15 +15852,15 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -15870,13 +15870,13 @@
       <c r="A67" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B67" s="8" t="n"/>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -15888,31 +15888,31 @@
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -15936,13 +15936,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -15956,7 +15956,7 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G72" s="8" t="n"/>
@@ -15964,17 +15964,17 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -16140,31 +16140,31 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B84" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -16176,13 +16176,13 @@
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
     </row>
@@ -16194,13 +16194,13 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="n"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -16470,7 +16470,7 @@
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -16486,7 +16486,7 @@
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -764,7 +764,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
@@ -796,15 +796,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -812,15 +812,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -828,7 +828,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -844,15 +844,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -860,11 +860,11 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -876,15 +876,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -892,7 +892,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -908,7 +908,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -956,15 +956,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -972,15 +972,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -988,15 +988,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -1004,11 +1004,11 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
@@ -1024,29 +1024,29 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B22" s="8" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -1054,63 +1054,63 @@
       <c r="A23" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B24" s="8" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -1148,11 +1148,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -1164,11 +1164,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -1180,15 +1180,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -1196,13 +1196,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1214,13 +1214,13 @@
       <c r="A33" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="8" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -1228,13 +1228,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1244,13 +1244,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1260,15 +1260,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -1278,13 +1278,13 @@
       <c r="A37" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B37" s="8" t="n"/>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -1308,15 +1308,15 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -1324,15 +1324,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -1342,13 +1342,13 @@
       <c r="A41" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -1356,15 +1356,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
@@ -1420,47 +1420,47 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B48" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
@@ -1550,13 +1550,13 @@
       <c r="A54" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B54" s="8" t="n"/>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -1570,7 +1570,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1598,13 +1598,13 @@
       <c r="A57" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -1612,13 +1612,13 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1634,7 +1634,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1650,7 +1650,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1662,13 +1662,13 @@
       <c r="A61" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="8" t="n"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -1682,7 +1682,7 @@
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C63" s="8" t="n"/>
@@ -1710,13 +1710,13 @@
       <c r="A64" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -1730,7 +1730,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1746,7 +1746,7 @@
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1774,13 +1774,13 @@
       <c r="A68" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -1794,7 +1794,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1804,15 +1804,15 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B70" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -1820,19 +1820,19 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -1844,7 +1844,7 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G72" s="8" t="n"/>
@@ -1852,17 +1852,17 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B73" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C75" s="8" t="n"/>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C76" s="8" t="n"/>
@@ -1918,13 +1918,13 @@
       <c r="A77" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+      <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
@@ -1938,7 +1938,7 @@
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -1954,7 +1954,7 @@
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -1970,7 +1970,7 @@
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -1984,15 +1984,15 @@
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -2512,7 +2512,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -2544,11 +2544,11 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -2560,11 +2560,11 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
@@ -2592,15 +2592,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -2610,13 +2610,13 @@
       <c r="A10" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -2624,11 +2624,11 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -2706,41 +2706,41 @@
       <c r="A16" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -2752,11 +2752,11 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
@@ -2800,15 +2800,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -2820,29 +2820,29 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B24" s="8" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -2850,37 +2850,37 @@
       <c r="A25" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -2896,11 +2896,11 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -2914,13 +2914,13 @@
       <c r="A29" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -2928,11 +2928,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -2960,15 +2960,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -2976,11 +2976,11 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -2992,35 +2992,35 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3046,7 +3046,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -3056,15 +3056,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -3072,11 +3072,11 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -3088,15 +3088,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -3110,7 +3110,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -3120,13 +3120,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -3136,13 +3136,13 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -3158,7 +3158,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -3168,15 +3168,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -3184,15 +3184,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B46" s="8" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -3200,15 +3200,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B47" s="8" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -3222,7 +3222,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -3232,15 +3232,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -3298,13 +3298,13 @@
       <c r="A53" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -3312,15 +3312,15 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B54" s="8" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -3328,19 +3328,19 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -3352,7 +3352,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G56" s="8" t="n"/>
@@ -3360,17 +3360,17 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
     </row>
@@ -3378,29 +3378,29 @@
       <c r="A58" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B59" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -3442,13 +3442,13 @@
       <c r="A62" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -3462,7 +3462,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -3476,15 +3476,15 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -3494,13 +3494,13 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -3514,65 +3514,65 @@
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
-      <c r="F69" s="8" t="n"/>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G69" s="8" t="n"/>
       <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -3584,11 +3584,11 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -3600,11 +3600,11 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C72" s="8" t="n"/>
@@ -3616,17 +3616,17 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B73" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -3634,29 +3634,29 @@
       <c r="A74" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B75" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
@@ -3680,7 +3680,7 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
@@ -3696,11 +3696,11 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -3712,11 +3712,11 @@
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -3728,11 +3728,11 @@
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -3744,15 +3744,15 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -3776,13 +3776,13 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -3792,13 +3792,13 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -3808,13 +3808,13 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -3824,13 +3824,13 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -3840,49 +3840,49 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="n"/>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
     </row>
@@ -3892,27 +3892,27 @@
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B91" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="8" t="n"/>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
@@ -4292,7 +4292,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -4326,13 +4326,13 @@
       <c r="A7" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -4340,15 +4340,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -4356,15 +4356,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -4374,13 +4374,13 @@
       <c r="A10" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -4390,13 +4390,13 @@
       <c r="A11" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B11" s="8" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -4404,15 +4404,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -4436,7 +4436,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -4484,11 +4484,11 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -4500,11 +4500,11 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -4516,11 +4516,11 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
@@ -4564,15 +4564,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -4584,29 +4584,29 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -4660,11 +4660,11 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -4678,13 +4678,13 @@
       <c r="A29" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -4724,15 +4724,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -4740,11 +4740,11 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -4810,7 +4810,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -4820,15 +4820,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -4838,13 +4838,13 @@
       <c r="A39" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -4852,7 +4852,7 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
@@ -4884,13 +4884,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -4900,13 +4900,13 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -4922,7 +4922,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -4932,15 +4932,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -4948,15 +4948,15 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B46" s="8" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -4964,15 +4964,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B47" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -4986,7 +4986,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -4996,15 +4996,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -5062,13 +5062,13 @@
       <c r="A53" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -5076,15 +5076,15 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B54" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -5092,19 +5092,19 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -5116,7 +5116,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G56" s="8" t="n"/>
@@ -5124,17 +5124,17 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
     </row>
@@ -5142,21 +5142,21 @@
       <c r="A58" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
@@ -5220,7 +5220,7 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
@@ -5252,7 +5252,7 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
@@ -5272,47 +5272,47 @@
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B68" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -5350,13 +5350,13 @@
       <c r="A71" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -5366,15 +5366,15 @@
       <c r="A72" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="n"/>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -5414,13 +5414,13 @@
       <c r="A75" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -5510,13 +5510,13 @@
       <c r="A81" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -5530,7 +5530,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -5546,7 +5546,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -5562,7 +5562,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -5592,13 +5592,13 @@
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
     </row>
@@ -5608,27 +5608,27 @@
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="n"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B88" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
@@ -5636,47 +5636,47 @@
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -6072,11 +6072,11 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -6088,11 +6088,11 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
@@ -6122,13 +6122,13 @@
       <c r="A9" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B9" s="8" t="n"/>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -6136,15 +6136,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -6152,11 +6152,11 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -6168,7 +6168,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -6248,11 +6248,11 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -6264,15 +6264,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -6296,15 +6296,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B20" s="8" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -6328,15 +6328,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -6348,29 +6348,29 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -6378,31 +6378,31 @@
       <c r="A25" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -6426,13 +6426,13 @@
       <c r="A28" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -6488,15 +6488,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -6504,11 +6504,11 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -6574,7 +6574,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -6584,15 +6584,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -6600,11 +6600,11 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -6616,15 +6616,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -6638,7 +6638,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -6648,13 +6648,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -6670,7 +6670,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -6686,7 +6686,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -6698,13 +6698,13 @@
       <c r="A45" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -6714,13 +6714,13 @@
       <c r="A46" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -6730,13 +6730,13 @@
       <c r="A47" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B47" s="8" t="n"/>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -6750,7 +6750,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -6760,15 +6760,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -6792,17 +6792,17 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -6810,13 +6810,13 @@
       <c r="A52" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -6826,29 +6826,29 @@
       <c r="A53" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B54" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -6856,19 +6856,19 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -6880,7 +6880,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G56" s="8" t="n"/>
@@ -6888,17 +6888,17 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
     </row>
@@ -6906,29 +6906,29 @@
       <c r="A58" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -6970,13 +6970,13 @@
       <c r="A62" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -6986,13 +6986,13 @@
       <c r="A63" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -7006,7 +7006,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -7020,13 +7020,13 @@
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
@@ -7038,13 +7038,13 @@
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -7058,7 +7058,7 @@
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -7074,25 +7074,25 @@
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -7148,29 +7148,29 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C75" s="8" t="n"/>
@@ -7194,13 +7194,13 @@
       <c r="A76" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -7214,7 +7214,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -7224,15 +7224,15 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B78" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -7274,13 +7274,13 @@
       <c r="A81" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -7294,7 +7294,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -7310,7 +7310,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -7450,13 +7450,13 @@
       <c r="A92" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B92" s="8" t="n"/>
       <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="8" t="n"/>
@@ -7468,15 +7468,15 @@
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -7484,75 +7484,75 @@
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D94" s="8" t="n"/>
       <c r="E94" s="8" t="n"/>
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B95" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="n"/>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
@@ -7564,27 +7564,27 @@
       </c>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="8" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
@@ -7838,13 +7838,13 @@
       <c r="A6" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B6" s="8" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -7852,13 +7852,13 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -7870,13 +7870,13 @@
       <c r="A8" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -7884,7 +7884,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -7900,15 +7900,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -7918,13 +7918,13 @@
       <c r="A11" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -7932,15 +7932,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -7950,13 +7950,13 @@
       <c r="A13" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -7966,13 +7966,13 @@
       <c r="A14" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B14" s="8" t="n"/>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -7980,15 +7980,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -7998,13 +7998,13 @@
       <c r="A16" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -8012,15 +8012,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -8028,11 +8028,11 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -8044,15 +8044,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -8060,13 +8060,13 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -8094,13 +8094,13 @@
       <c r="A22" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B22" s="8" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -8124,11 +8124,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -8142,31 +8142,31 @@
       <c r="A25" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -8188,15 +8188,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -8204,15 +8204,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -8236,11 +8236,11 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -8252,7 +8252,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
@@ -8268,7 +8268,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
@@ -8284,13 +8284,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -8302,13 +8302,13 @@
       <c r="A35" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -8316,15 +8316,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B36" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -8332,15 +8332,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -8350,13 +8350,13 @@
       <c r="A38" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -8364,13 +8364,13 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -8382,13 +8382,13 @@
       <c r="A40" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -8400,41 +8400,41 @@
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -8444,13 +8444,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -8466,7 +8466,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -8476,7 +8476,7 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
@@ -8492,7 +8492,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -8684,15 +8684,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B59" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -8700,65 +8700,65 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
@@ -8770,7 +8770,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -8786,7 +8786,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -8800,15 +8800,15 @@
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -9584,7 +9584,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -9602,13 +9602,13 @@
       <c r="A6" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B6" s="8" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -9616,13 +9616,13 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -9634,13 +9634,13 @@
       <c r="A8" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -9648,7 +9648,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -9680,7 +9680,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -9696,15 +9696,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -9712,15 +9712,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -9760,15 +9760,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -9776,15 +9776,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -9792,11 +9792,11 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -9808,11 +9808,11 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
@@ -9844,31 +9844,31 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -9888,11 +9888,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -9952,15 +9952,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -9968,15 +9968,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -10000,11 +10000,11 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -10016,7 +10016,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
@@ -10054,7 +10054,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -10064,15 +10064,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -10082,13 +10082,13 @@
       <c r="A36" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -10096,15 +10096,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -10114,13 +10114,13 @@
       <c r="A38" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -10128,13 +10128,13 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -10146,13 +10146,13 @@
       <c r="A40" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -10164,31 +10164,31 @@
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -10198,7 +10198,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -10214,7 +10214,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -10224,13 +10224,13 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -10448,15 +10448,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B59" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -10464,65 +10464,65 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
@@ -10534,7 +10534,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -10550,7 +10550,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -10564,15 +10564,15 @@
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -10676,15 +10676,15 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -10694,13 +10694,13 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -10714,41 +10714,41 @@
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B76" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B77" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -10786,13 +10786,13 @@
       <c r="A80" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B80" s="8" t="n"/>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
@@ -10802,13 +10802,13 @@
       <c r="A81" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -10822,7 +10822,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -10836,13 +10836,13 @@
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
     </row>
@@ -11348,7 +11348,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -11366,13 +11366,13 @@
       <c r="A6" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B6" s="8" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -11380,13 +11380,13 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -11398,13 +11398,13 @@
       <c r="A8" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -11412,7 +11412,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -11460,15 +11460,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -11476,15 +11476,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -11494,13 +11494,13 @@
       <c r="A14" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B14" s="8" t="n"/>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -11508,15 +11508,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -11524,15 +11524,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -11540,15 +11540,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -11556,11 +11556,11 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -11572,15 +11572,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -11588,13 +11588,13 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -11622,13 +11622,13 @@
       <c r="A22" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B22" s="8" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -11652,11 +11652,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -11670,31 +11670,31 @@
       <c r="A25" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -11716,15 +11716,15 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
@@ -11732,15 +11732,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -11764,11 +11764,11 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -11780,7 +11780,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
@@ -11818,7 +11818,7 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -11828,15 +11828,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -11846,13 +11846,13 @@
       <c r="A36" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -11860,15 +11860,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -11878,13 +11878,13 @@
       <c r="A38" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -11892,13 +11892,13 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -11910,13 +11910,13 @@
       <c r="A40" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -11928,41 +11928,41 @@
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -11972,13 +11972,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -11994,7 +11994,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -12020,7 +12020,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
@@ -12052,7 +12052,7 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
@@ -12068,17 +12068,17 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B50" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -12086,13 +12086,13 @@
       <c r="A51" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -12104,13 +12104,13 @@
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
     </row>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -12212,15 +12212,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B59" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -12228,47 +12228,47 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B62" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -12276,15 +12276,15 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B63" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -12292,15 +12292,15 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B64" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -12308,33 +12308,33 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
     </row>
@@ -12342,13 +12342,13 @@
       <c r="A67" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -12358,13 +12358,13 @@
       <c r="A68" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -12374,13 +12374,13 @@
       <c r="A69" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -12394,7 +12394,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -12410,7 +12410,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -12424,15 +12424,15 @@
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="n"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -13096,7 +13096,7 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -13146,13 +13146,13 @@
       <c r="A7" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B7" s="8" t="n"/>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -13160,15 +13160,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -13176,7 +13176,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -13192,15 +13192,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -13208,11 +13208,11 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -13224,15 +13224,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -13256,7 +13256,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -13272,15 +13272,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -13288,15 +13288,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -13306,13 +13306,13 @@
       <c r="A17" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -13322,13 +13322,13 @@
       <c r="A18" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -13336,15 +13336,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
@@ -13372,29 +13372,29 @@
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B22" s="8" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
@@ -13402,33 +13402,33 @@
       <c r="A23" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B24" s="8" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -13480,7 +13480,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -13496,11 +13496,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -13512,11 +13512,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -13528,15 +13528,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -13544,13 +13544,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -13562,13 +13562,13 @@
       <c r="A33" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="8" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -13576,13 +13576,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -13598,7 +13598,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -13610,13 +13610,13 @@
       <c r="A36" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -13624,15 +13624,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B37" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -13656,15 +13656,15 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -13672,15 +13672,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -13690,13 +13690,13 @@
       <c r="A41" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -13704,15 +13704,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
@@ -13772,35 +13772,35 @@
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
@@ -13864,7 +13864,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
@@ -13898,13 +13898,13 @@
       <c r="A54" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B54" s="8" t="n"/>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -13918,7 +13918,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -13946,13 +13946,13 @@
       <c r="A57" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -13960,13 +13960,13 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -13982,7 +13982,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -13998,7 +13998,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -14026,13 +14026,13 @@
       <c r="A62" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B62" s="8" t="n"/>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -14046,7 +14046,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -14062,7 +14062,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -14072,15 +14072,15 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
@@ -14122,13 +14122,13 @@
       <c r="A68" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -14142,7 +14142,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -14152,15 +14152,15 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -14168,19 +14168,19 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -14192,7 +14192,7 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G72" s="8" t="n"/>
@@ -14200,17 +14200,17 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -14222,7 +14222,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -14238,7 +14238,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -14252,15 +14252,15 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="n"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -14876,7 +14876,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
@@ -14908,15 +14908,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -14924,15 +14924,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -14940,7 +14940,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -14956,15 +14956,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>59</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -14972,11 +14972,11 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -14988,15 +14988,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -15004,7 +15004,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -15020,7 +15020,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -15068,15 +15068,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -15084,15 +15084,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -15100,15 +15100,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B19" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -15116,11 +15116,11 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
@@ -15132,7 +15132,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -15148,15 +15148,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B22" s="8" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -15166,63 +15166,63 @@
       <c r="A23" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -15244,7 +15244,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -15260,11 +15260,11 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -15276,11 +15276,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -15292,15 +15292,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -15308,13 +15308,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -15342,13 +15342,13 @@
       <c r="A34" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -15356,13 +15356,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -15372,15 +15372,15 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -15390,13 +15390,13 @@
       <c r="A37" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="8" t="n"/>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -15420,15 +15420,15 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -15438,13 +15438,13 @@
       <c r="A40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
@@ -15484,15 +15484,15 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B43" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -15502,13 +15502,13 @@
       <c r="A44" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -15522,7 +15522,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -15534,21 +15534,21 @@
       <c r="A46" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
@@ -15564,23 +15564,23 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B48" s="8" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
@@ -15628,7 +15628,7 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
@@ -15662,13 +15662,13 @@
       <c r="A54" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="8" t="n"/>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -15682,7 +15682,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -15710,13 +15710,13 @@
       <c r="A57" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -15724,13 +15724,13 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -15746,7 +15746,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -15762,7 +15762,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -15806,13 +15806,13 @@
       <c r="A63" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -15826,7 +15826,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -15842,7 +15842,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -15852,15 +15852,15 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -15870,13 +15870,13 @@
       <c r="A67" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -15884,15 +15884,15 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -15900,19 +15900,19 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -15922,7 +15922,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -15936,13 +15936,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -15956,7 +15956,7 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G72" s="8" t="n"/>
@@ -15964,19 +15964,19 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -16140,31 +16140,31 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="8" t="n"/>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -16176,13 +16176,13 @@
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
     </row>
@@ -16194,13 +16194,13 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -764,7 +764,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
@@ -796,15 +796,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -812,15 +812,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>67</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -828,7 +828,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -844,7 +844,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -908,7 +908,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -926,13 +926,13 @@
       <c r="A15" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B15" s="8" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -940,15 +940,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -956,7 +956,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -1054,63 +1054,63 @@
       <c r="A23" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -1122,7 +1122,7 @@
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1132,13 +1132,13 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1166,13 +1166,13 @@
       <c r="A30" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -1196,15 +1196,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -1228,13 +1228,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1250,7 +1250,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1292,15 +1292,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -1308,13 +1308,13 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1324,11 +1324,11 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C40" s="8" t="n"/>
@@ -1342,13 +1342,13 @@
       <c r="A41" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -1362,7 +1362,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1374,13 +1374,13 @@
       <c r="A43" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -1394,7 +1394,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1404,15 +1404,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -1422,13 +1422,13 @@
       <c r="A46" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -1440,31 +1440,31 @@
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -1532,7 +1532,7 @@
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
@@ -1550,13 +1550,13 @@
       <c r="A54" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -1570,7 +1570,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1598,13 +1598,13 @@
       <c r="A57" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B57" s="8" t="n"/>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -1612,13 +1612,13 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1644,15 +1644,15 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B60" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
@@ -1662,13 +1662,13 @@
       <c r="A61" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -1682,7 +1682,7 @@
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1772,19 +1772,19 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -1794,7 +1794,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1804,15 +1804,15 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -1822,15 +1822,15 @@
       <c r="A71" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B71" s="8" t="n"/>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -1844,7 +1844,7 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G72" s="8" t="n"/>
@@ -1852,17 +1852,17 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C75" s="8" t="n"/>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C76" s="8" t="n"/>
@@ -1918,13 +1918,13 @@
       <c r="A77" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B77" s="8" t="n"/>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
@@ -1938,7 +1938,7 @@
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -1954,7 +1954,7 @@
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -1970,7 +1970,7 @@
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -1984,15 +1984,15 @@
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C91" s="8" t="n"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -2560,15 +2560,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -2578,13 +2578,13 @@
       <c r="A8" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B8" s="8" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -2592,15 +2592,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -2610,13 +2610,13 @@
       <c r="A10" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -2818,31 +2818,31 @@
       <c r="A23" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -2850,31 +2850,31 @@
       <c r="A25" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -2928,11 +2928,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -2944,11 +2944,11 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C32" s="8" t="n"/>
@@ -2996,31 +2996,31 @@
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3030,7 +3030,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -3046,7 +3046,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -3056,15 +3056,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -3090,13 +3090,13 @@
       <c r="A40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
@@ -3142,7 +3142,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -3158,7 +3158,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -3168,15 +3168,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -3186,13 +3186,13 @@
       <c r="A46" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -3280,31 +3280,31 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -3312,15 +3312,15 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -3330,15 +3330,15 @@
       <c r="A55" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -3352,7 +3352,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G56" s="8" t="n"/>
@@ -3360,17 +3360,17 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
     </row>
@@ -3378,17 +3378,17 @@
       <c r="A58" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B58" s="8" t="n"/>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -3636,29 +3636,29 @@
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="n"/>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
     </row>
@@ -3666,13 +3666,13 @@
       <c r="A76" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -3686,7 +3686,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -3696,15 +3696,15 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -3746,13 +3746,13 @@
       <c r="A81" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B81" s="8" t="n"/>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -3782,7 +3782,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -3798,7 +3798,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -3814,7 +3814,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -3830,7 +3830,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -3846,7 +3846,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -3860,13 +3860,13 @@
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
     </row>
@@ -3878,41 +3878,41 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B90" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C90" s="8" t="n"/>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -3970,13 +3970,13 @@
       <c r="A95" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B95" s="8" t="n"/>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
@@ -3990,7 +3990,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -4006,7 +4006,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -4020,31 +4020,31 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -4308,11 +4308,11 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
@@ -4340,11 +4340,11 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
@@ -4356,15 +4356,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -4374,13 +4374,13 @@
       <c r="A10" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -4614,37 +4614,37 @@
       <c r="A25" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -4692,11 +4692,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -4708,11 +4708,11 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C32" s="8" t="n"/>
@@ -4756,13 +4756,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -4776,31 +4776,31 @@
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -4810,7 +4810,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -4820,15 +4820,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -4854,13 +4854,13 @@
       <c r="A40" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -4884,7 +4884,7 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
@@ -4906,7 +4906,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -4922,7 +4922,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -4932,15 +4932,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -4950,13 +4950,13 @@
       <c r="A46" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -5044,31 +5044,31 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -5076,15 +5076,15 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -5094,15 +5094,15 @@
       <c r="A55" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -5116,7 +5116,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G56" s="8" t="n"/>
@@ -5124,17 +5124,17 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
     </row>
@@ -5142,17 +5142,17 @@
       <c r="A58" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B58" s="8" t="n"/>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -5302,13 +5302,13 @@
       <c r="A68" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -5318,25 +5318,25 @@
       <c r="A69" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
-      <c r="F69" s="8" t="n"/>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G69" s="8" t="n"/>
       <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -5348,15 +5348,15 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B71" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -5364,33 +5364,33 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B72" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B73" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -5398,13 +5398,13 @@
       <c r="A74" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
@@ -5414,13 +5414,13 @@
       <c r="A75" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -5434,7 +5434,7 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -5448,13 +5448,13 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -5510,13 +5510,13 @@
       <c r="A81" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B81" s="8" t="n"/>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -5530,7 +5530,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -5546,7 +5546,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -5562,7 +5562,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -5592,13 +5592,13 @@
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
     </row>
@@ -5610,41 +5610,41 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B89" s="8" t="n"/>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
@@ -5674,7 +5674,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -5734,13 +5734,13 @@
       <c r="A95" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B95" s="8" t="n"/>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
@@ -5754,7 +5754,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -5770,7 +5770,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -5784,31 +5784,31 @@
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -6088,15 +6088,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -6106,13 +6106,13 @@
       <c r="A8" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B8" s="8" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -6120,15 +6120,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -6138,13 +6138,13 @@
       <c r="A10" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -6168,7 +6168,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -6360,7 +6360,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -6378,37 +6378,37 @@
       <c r="A25" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -6456,11 +6456,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -6472,11 +6472,11 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C32" s="8" t="n"/>
@@ -6520,13 +6520,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -6540,31 +6540,31 @@
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -6574,7 +6574,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -6584,15 +6584,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -6618,13 +6618,13 @@
       <c r="A40" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
@@ -6670,7 +6670,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -6680,15 +6680,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B44" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -6714,13 +6714,13 @@
       <c r="A46" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -6792,31 +6792,31 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="8" t="n"/>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -6828,29 +6828,29 @@
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
@@ -6858,15 +6858,15 @@
       <c r="A55" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -6880,7 +6880,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G56" s="8" t="n"/>
@@ -6888,17 +6888,17 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
     </row>
@@ -6906,17 +6906,17 @@
       <c r="A58" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B58" s="8" t="n"/>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -7022,13 +7022,13 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -7042,7 +7042,7 @@
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -7058,25 +7058,25 @@
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B68" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -7152,7 +7152,7 @@
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G73" s="8" t="n"/>
@@ -7160,17 +7160,17 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C75" s="8" t="n"/>
@@ -7198,7 +7198,7 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -7214,7 +7214,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -7224,15 +7224,15 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -7274,13 +7274,13 @@
       <c r="A81" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="8" t="n"/>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -7310,7 +7310,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -7326,7 +7326,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -7342,7 +7342,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -7358,7 +7358,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -7374,7 +7374,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -7388,13 +7388,13 @@
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
     </row>
@@ -7406,41 +7406,41 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C90" s="8" t="n"/>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C95" s="8" t="n"/>
@@ -7514,13 +7514,13 @@
       <c r="A96" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B96" s="8" t="n"/>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
@@ -7534,7 +7534,7 @@
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -7550,7 +7550,7 @@
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -7564,31 +7564,31 @@
       </c>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="n"/>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
       <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -7838,13 +7838,13 @@
       <c r="A6" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -7852,13 +7852,13 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -7868,15 +7868,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -7884,7 +7884,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -7900,15 +7900,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -7918,13 +7918,13 @@
       <c r="A11" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B11" s="8" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -8028,15 +8028,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -8046,13 +8046,13 @@
       <c r="A19" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B19" s="8" t="n"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -8124,7 +8124,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -8142,37 +8142,37 @@
       <c r="A25" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -8220,11 +8220,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -8236,15 +8236,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -8254,13 +8254,13 @@
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="n"/>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -8268,15 +8268,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -8286,13 +8286,13 @@
       <c r="A34" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -8300,15 +8300,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B35" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -8318,13 +8318,13 @@
       <c r="A36" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
@@ -8338,7 +8338,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -8400,41 +8400,41 @@
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -8444,13 +8444,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -8466,7 +8466,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -8636,19 +8636,19 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -8684,15 +8684,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -8702,15 +8702,15 @@
       <c r="A60" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B60" s="8" t="n"/>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -8718,47 +8718,47 @@
       <c r="A61" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B61" s="8" t="n"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
@@ -8770,7 +8770,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -8786,7 +8786,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -8796,19 +8796,19 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -8846,13 +8846,13 @@
       <c r="A69" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -8866,7 +8866,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -8958,13 +8958,13 @@
       <c r="A76" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -8976,29 +8976,29 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -9054,13 +9054,13 @@
       <c r="A82" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B82" s="8" t="n"/>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
@@ -9074,7 +9074,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -9088,29 +9088,29 @@
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
     </row>
@@ -9602,13 +9602,13 @@
       <c r="A6" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -9616,13 +9616,13 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -9632,15 +9632,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -9648,7 +9648,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -9680,7 +9680,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -9792,15 +9792,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -9826,13 +9826,13 @@
       <c r="A20" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B20" s="8" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -9888,7 +9888,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -9906,37 +9906,37 @@
       <c r="A25" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -9984,11 +9984,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -10000,15 +10000,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -10018,13 +10018,13 @@
       <c r="A32" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="8" t="n"/>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -10032,15 +10032,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -10050,13 +10050,13 @@
       <c r="A34" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -10064,13 +10064,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -10080,7 +10080,7 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
@@ -10096,13 +10096,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -10164,41 +10164,41 @@
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -10208,13 +10208,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -10230,7 +10230,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -10242,13 +10242,13 @@
       <c r="A46" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -10256,15 +10256,15 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -10400,19 +10400,19 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -10448,15 +10448,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -10466,15 +10466,15 @@
       <c r="A60" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B60" s="8" t="n"/>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -10482,47 +10482,47 @@
       <c r="A61" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="8" t="n"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
@@ -10534,7 +10534,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -10550,7 +10550,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -10560,19 +10560,19 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -10610,13 +10610,13 @@
       <c r="A69" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -10630,7 +10630,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -10786,13 +10786,13 @@
       <c r="A80" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B80" s="8" t="n"/>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
@@ -10806,7 +10806,7 @@
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -10822,7 +10822,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -10836,13 +10836,13 @@
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
     </row>
@@ -10856,7 +10856,7 @@
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G84" s="8" t="n"/>
@@ -10864,17 +10864,17 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
     </row>
@@ -11366,13 +11366,13 @@
       <c r="A6" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -11380,13 +11380,13 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -11396,15 +11396,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -11412,7 +11412,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -11492,7 +11492,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -11556,15 +11556,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -11574,13 +11574,13 @@
       <c r="A19" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B19" s="8" t="n"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -11652,7 +11652,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -11670,37 +11670,37 @@
       <c r="A25" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -11748,11 +11748,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -11764,15 +11764,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -11782,13 +11782,13 @@
       <c r="A32" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="8" t="n"/>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -11796,15 +11796,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -11814,13 +11814,13 @@
       <c r="A34" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -11828,13 +11828,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -11844,7 +11844,7 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
@@ -11860,13 +11860,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -11928,41 +11928,41 @@
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -11972,13 +11972,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -11994,7 +11994,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -12020,7 +12020,7 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
@@ -12164,19 +12164,19 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -12212,15 +12212,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -12230,15 +12230,15 @@
       <c r="A60" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B60" s="8" t="n"/>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -12246,47 +12246,47 @@
       <c r="A61" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="8" t="n"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C64" s="8" t="n"/>
@@ -12310,13 +12310,13 @@
       <c r="A65" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B65" s="8" t="n"/>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
@@ -12326,13 +12326,13 @@
       <c r="A66" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -12346,7 +12346,7 @@
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -12362,7 +12362,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -12394,7 +12394,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -12410,7 +12410,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -12424,15 +12424,15 @@
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -12470,13 +12470,13 @@
       <c r="A75" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -12488,13 +12488,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -12506,29 +12506,29 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -12582,13 +12582,13 @@
       <c r="A82" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B82" s="8" t="n"/>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
@@ -12602,7 +12602,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -12616,29 +12616,29 @@
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
     </row>
@@ -13146,13 +13146,13 @@
       <c r="A7" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -13160,15 +13160,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -13176,7 +13176,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -13192,7 +13192,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -13304,7 +13304,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -13402,33 +13402,33 @@
       <c r="A23" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -13450,13 +13450,13 @@
       <c r="A26" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -13464,15 +13464,15 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B27" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -13480,13 +13480,13 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -13496,7 +13496,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
@@ -13512,15 +13512,15 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -13530,13 +13530,13 @@
       <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="8" t="n"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -13550,7 +13550,7 @@
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -13576,13 +13576,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -13598,7 +13598,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -13640,7 +13640,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -13656,15 +13656,15 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B39" s="8" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -13672,7 +13672,7 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
@@ -13690,13 +13690,13 @@
       <c r="A41" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -13710,7 +13710,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -13722,13 +13722,13 @@
       <c r="A43" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -13742,7 +13742,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -13752,15 +13752,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B45" s="8" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -13786,13 +13786,13 @@
       <c r="A47" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B47" s="8" t="n"/>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -13800,15 +13800,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -13898,13 +13898,13 @@
       <c r="A54" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -13918,7 +13918,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -13946,13 +13946,13 @@
       <c r="A57" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B57" s="8" t="n"/>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -13960,13 +13960,13 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -13992,13 +13992,13 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -14014,7 +14014,7 @@
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -14042,13 +14042,13 @@
       <c r="A63" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -14062,7 +14062,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -14078,7 +14078,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -14088,15 +14088,15 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -14120,19 +14120,19 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -14142,7 +14142,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -14152,15 +14152,15 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -14170,15 +14170,15 @@
       <c r="A71" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="8" t="n"/>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -14192,7 +14192,7 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G72" s="8" t="n"/>
@@ -14200,17 +14200,17 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -14222,7 +14222,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -14238,7 +14238,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -14252,15 +14252,15 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -14490,31 +14490,31 @@
       <c r="A91" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B91" s="8" t="n"/>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B92" s="8" t="n"/>
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
-      <c r="F92" s="8" t="n"/>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G92" s="8" t="n"/>
       <c r="H92" s="8" t="n"/>
     </row>
@@ -14892,7 +14892,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
@@ -14908,15 +14908,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -14924,15 +14924,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -14940,7 +14940,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
@@ -14956,7 +14956,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -15020,7 +15020,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -15038,13 +15038,13 @@
       <c r="A15" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B15" s="8" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -15052,15 +15052,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -15068,7 +15068,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -15166,63 +15166,63 @@
       <c r="A23" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -15234,7 +15234,7 @@
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -15244,13 +15244,13 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -15278,13 +15278,13 @@
       <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
@@ -15308,15 +15308,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -15324,15 +15324,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="8" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -15342,13 +15342,13 @@
       <c r="A34" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -15362,7 +15362,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -15404,15 +15404,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -15420,13 +15420,13 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -15436,11 +15436,11 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C40" s="8" t="n"/>
@@ -15454,13 +15454,13 @@
       <c r="A41" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -15474,7 +15474,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -15550,13 +15550,13 @@
       <c r="A47" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B47" s="8" t="n"/>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -15564,15 +15564,15 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -15662,13 +15662,13 @@
       <c r="A54" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -15682,7 +15682,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -15710,13 +15710,13 @@
       <c r="A57" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="8" t="n"/>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -15724,13 +15724,13 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -15756,15 +15756,15 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
@@ -15788,15 +15788,15 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -15806,13 +15806,13 @@
       <c r="A63" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -15826,7 +15826,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -15842,7 +15842,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -15852,15 +15852,15 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -15868,31 +15868,31 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="n"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -15902,13 +15902,13 @@
       <c r="A69" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B69" s="8" t="n"/>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -15922,7 +15922,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -15936,13 +15936,13 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -15956,7 +15956,7 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G72" s="8" t="n"/>
@@ -15964,19 +15964,19 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -16254,31 +16254,31 @@
       <c r="A91" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B91" s="8" t="n"/>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B92" s="8" t="n"/>
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
-      <c r="F92" s="8" t="n"/>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G92" s="8" t="n"/>
       <c r="H92" s="8" t="n"/>
     </row>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -860,15 +860,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -876,15 +876,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>59</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -892,7 +892,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -908,7 +908,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -924,15 +924,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -940,15 +940,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -956,13 +956,13 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -978,7 +978,7 @@
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -1052,11 +1052,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -1070,53 +1070,53 @@
       <c r="A24" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -1218,7 +1218,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1228,13 +1228,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1244,13 +1244,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1266,7 +1266,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1276,15 +1276,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -1294,13 +1294,13 @@
       <c r="A38" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -1324,15 +1324,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -1340,11 +1340,11 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
@@ -1356,15 +1356,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -1404,13 +1404,13 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1420,13 +1420,13 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1440,43 +1440,43 @@
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -1564,15 +1564,15 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -1582,13 +1582,13 @@
       <c r="A56" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -1602,7 +1602,7 @@
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1618,7 +1618,7 @@
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1634,7 +1634,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1650,7 +1650,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1660,15 +1660,15 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -1678,13 +1678,13 @@
       <c r="A62" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B62" s="8" t="n"/>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -1788,31 +1788,31 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B70" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -1822,15 +1822,15 @@
       <c r="A71" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -1842,13 +1842,13 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="n"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -1924,7 +1924,7 @@
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G77" s="8" t="n"/>
@@ -1932,17 +1932,17 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C82" s="8" t="n"/>
@@ -2014,13 +2014,13 @@
       <c r="A83" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="8" t="n"/>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
@@ -2034,7 +2034,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2048,13 +2048,13 @@
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
     </row>
@@ -2578,13 +2578,13 @@
       <c r="A8" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B8" s="8" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -2598,7 +2598,7 @@
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -2608,15 +2608,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -2640,15 +2640,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -2656,15 +2656,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
@@ -2768,15 +2768,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -2786,13 +2786,13 @@
       <c r="A21" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B21" s="8" t="n"/>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -2806,7 +2806,7 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -2818,69 +2818,69 @@
       <c r="A23" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B24" s="8" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -2896,11 +2896,11 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -2912,15 +2912,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -2946,13 +2946,13 @@
       <c r="A31" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -3030,7 +3030,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -3040,13 +3040,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -3056,15 +3056,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -3090,13 +3090,13 @@
       <c r="A40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -3110,7 +3110,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -3152,13 +3152,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -3168,15 +3168,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -3186,13 +3186,13 @@
       <c r="A46" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -3236,43 +3236,43 @@
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -3280,31 +3280,31 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -3312,15 +3312,15 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B54" s="8" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -3330,15 +3330,15 @@
       <c r="A55" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -3352,7 +3352,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G56" s="8" t="n"/>
@@ -3376,19 +3376,19 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C59" s="8" t="n"/>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C62" s="8" t="n"/>
@@ -3458,13 +3458,13 @@
       <c r="A63" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -3476,15 +3476,15 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -3498,25 +3498,25 @@
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -3638,7 +3638,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -3680,17 +3680,17 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B77" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -3730,13 +3730,13 @@
       <c r="A80" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B80" s="8" t="n"/>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
@@ -3750,7 +3750,7 @@
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -3766,7 +3766,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -3782,7 +3782,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -3798,7 +3798,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -3812,13 +3812,13 @@
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
     </row>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -4404,15 +4404,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -4420,15 +4420,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -4436,7 +4436,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -4456,31 +4456,31 @@
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -4516,7 +4516,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
@@ -4532,15 +4532,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -4548,15 +4548,15 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B21" s="8" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -4570,7 +4570,7 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -4596,11 +4596,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -4612,39 +4612,39 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -4660,11 +4660,11 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -4676,15 +4676,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -4692,11 +4692,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -4726,13 +4726,13 @@
       <c r="A32" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -4794,7 +4794,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -4804,13 +4804,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -4874,7 +4874,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -4916,13 +4916,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -4932,15 +4932,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -4950,13 +4950,13 @@
       <c r="A46" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -5000,43 +5000,43 @@
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -5044,27 +5044,27 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -5076,13 +5076,13 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -5094,15 +5094,15 @@
       <c r="A55" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -5116,7 +5116,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G56" s="8" t="n"/>
@@ -5140,19 +5140,19 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C59" s="8" t="n"/>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C62" s="8" t="n"/>
@@ -5222,13 +5222,13 @@
       <c r="A63" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -5240,15 +5240,15 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -5262,25 +5262,25 @@
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -5402,7 +5402,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -5444,17 +5444,17 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B77" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -5494,13 +5494,13 @@
       <c r="A80" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B80" s="8" t="n"/>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
@@ -5514,7 +5514,7 @@
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -5530,7 +5530,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -5546,7 +5546,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -5562,7 +5562,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -5594,7 +5594,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -5608,13 +5608,13 @@
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
@@ -6106,13 +6106,13 @@
       <c r="A8" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B8" s="8" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -6120,15 +6120,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -6168,15 +6168,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -6184,15 +6184,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
@@ -6232,7 +6232,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -6264,15 +6264,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -6282,13 +6282,13 @@
       <c r="A19" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -6296,15 +6296,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -6312,15 +6312,15 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B21" s="8" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -6334,7 +6334,7 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -6360,11 +6360,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -6376,39 +6376,39 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -6424,11 +6424,11 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -6440,15 +6440,15 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -6456,11 +6456,11 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -6490,13 +6490,13 @@
       <c r="A32" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -6558,7 +6558,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -6568,13 +6568,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -6638,7 +6638,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -6680,13 +6680,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -6696,15 +6696,15 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -6714,13 +6714,13 @@
       <c r="A46" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -6744,13 +6744,13 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -6760,17 +6760,17 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
@@ -6780,43 +6780,43 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -6824,15 +6824,15 @@
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B53" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -6840,13 +6840,13 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -6858,15 +6858,15 @@
       <c r="A55" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -6878,13 +6878,13 @@
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -6992,7 +6992,7 @@
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G63" s="8" t="n"/>
@@ -7006,13 +7006,13 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -7026,25 +7026,25 @@
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -7128,15 +7128,15 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C73" s="8" t="n"/>
@@ -7162,13 +7162,13 @@
       <c r="A74" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B74" s="8" t="n"/>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
@@ -7182,7 +7182,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -7198,7 +7198,7 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -7212,45 +7212,45 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B78" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
     </row>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -7274,13 +7274,13 @@
       <c r="A81" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -7290,13 +7290,13 @@
       <c r="A82" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
@@ -7310,7 +7310,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -7326,7 +7326,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -7342,7 +7342,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -7358,7 +7358,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -7374,7 +7374,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -7390,7 +7390,7 @@
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -7406,7 +7406,7 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -7420,13 +7420,13 @@
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
-      <c r="F90" s="8" t="n"/>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="n"/>
     </row>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -7964,7 +7964,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -7996,15 +7996,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B16" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -8014,13 +8014,13 @@
       <c r="A17" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -8028,35 +8028,35 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
@@ -8078,13 +8078,13 @@
       <c r="A21" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B21" s="8" t="n"/>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -8098,7 +8098,7 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -8124,11 +8124,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -8142,37 +8142,37 @@
       <c r="A25" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -8188,7 +8188,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -8270,13 +8270,13 @@
       <c r="A33" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -8284,15 +8284,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -8322,7 +8322,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -8348,15 +8348,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -8366,13 +8366,13 @@
       <c r="A39" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -8444,13 +8444,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -8466,7 +8466,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -8498,7 +8498,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -8514,7 +8514,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -8524,17 +8524,17 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
@@ -8544,13 +8544,13 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -8620,19 +8620,19 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -8654,13 +8654,13 @@
       <c r="A57" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -8668,15 +8668,15 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B58" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -8684,13 +8684,13 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -8702,13 +8702,13 @@
       <c r="A60" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
@@ -8732,19 +8732,19 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -8820,7 +8820,7 @@
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G67" s="8" t="n"/>
@@ -8828,17 +8828,17 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="n"/>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -8894,13 +8894,13 @@
       <c r="A72" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B72" s="8" t="n"/>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -8914,7 +8914,7 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -8930,7 +8930,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -8944,15 +8944,15 @@
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -8966,7 +8966,7 @@
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
@@ -8982,37 +8982,37 @@
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B79" s="8" t="n"/>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -9024,13 +9024,13 @@
       </c>
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E80" s="8" t="n"/>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
       <c r="H80" s="8" t="n"/>
     </row>
@@ -9148,17 +9148,17 @@
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B88" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -9198,13 +9198,13 @@
       <c r="A91" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -9218,7 +9218,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -9234,7 +9234,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -9250,7 +9250,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -9266,7 +9266,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -9282,7 +9282,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -9296,13 +9296,13 @@
       </c>
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
-      <c r="F97" s="8" t="n"/>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G97" s="8" t="n"/>
       <c r="H97" s="8" t="n"/>
     </row>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -9760,15 +9760,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B16" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -9778,13 +9778,13 @@
       <c r="A17" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -9792,15 +9792,15 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -9810,13 +9810,13 @@
       <c r="A19" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B19" s="8" t="n"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -9830,7 +9830,7 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -9888,11 +9888,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -9904,39 +9904,39 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -10034,13 +10034,13 @@
       <c r="A33" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -10048,15 +10048,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -10070,7 +10070,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -10112,15 +10112,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -10130,13 +10130,13 @@
       <c r="A39" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -10208,13 +10208,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -10230,7 +10230,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -10246,7 +10246,7 @@
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -10278,7 +10278,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -10288,17 +10288,17 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
@@ -10308,13 +10308,13 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -10384,19 +10384,19 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -10418,13 +10418,13 @@
       <c r="A57" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -10432,15 +10432,15 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B58" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -10448,13 +10448,13 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -10466,13 +10466,13 @@
       <c r="A60" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
@@ -10496,19 +10496,19 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -10584,7 +10584,7 @@
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G67" s="8" t="n"/>
@@ -10592,17 +10592,17 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="n"/>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -10658,13 +10658,13 @@
       <c r="A72" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="8" t="n"/>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -10678,7 +10678,7 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -10694,7 +10694,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -10708,15 +10708,15 @@
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -10730,7 +10730,7 @@
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
@@ -10746,25 +10746,25 @@
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -10802,13 +10802,13 @@
       <c r="A81" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B81" s="8" t="n"/>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -10822,7 +10822,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -10838,7 +10838,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -10852,13 +10852,13 @@
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
     </row>
@@ -10912,17 +10912,17 @@
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B88" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
     </row>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -10962,13 +10962,13 @@
       <c r="A91" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -10982,7 +10982,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -10998,7 +10998,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -11014,7 +11014,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -11030,7 +11030,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -11046,7 +11046,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -11060,13 +11060,13 @@
       </c>
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
-      <c r="F97" s="8" t="n"/>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G97" s="8" t="n"/>
       <c r="H97" s="8" t="n"/>
     </row>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -11492,7 +11492,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -11524,15 +11524,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B16" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -11542,13 +11542,13 @@
       <c r="A17" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -11556,47 +11556,47 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B20" s="8" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -11610,7 +11610,7 @@
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -11652,11 +11652,11 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -11668,39 +11668,39 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -11716,7 +11716,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -11798,13 +11798,13 @@
       <c r="A33" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -11812,15 +11812,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -11834,7 +11834,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -11876,15 +11876,15 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -11894,13 +11894,13 @@
       <c r="A39" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -11972,13 +11972,13 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -11994,7 +11994,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -12010,7 +12010,7 @@
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -12042,7 +12042,7 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -12052,17 +12052,17 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
@@ -12072,13 +12072,13 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -12148,19 +12148,19 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -12182,13 +12182,13 @@
       <c r="A57" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -12196,15 +12196,15 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B58" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -12212,13 +12212,13 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -12230,13 +12230,13 @@
       <c r="A60" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
@@ -12260,19 +12260,19 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C63" s="8" t="n"/>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C64" s="8" t="n"/>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -12326,13 +12326,13 @@
       <c r="A66" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -12460,7 +12460,7 @@
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G74" s="8" t="n"/>
@@ -12474,13 +12474,13 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="n"/>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -12494,37 +12494,37 @@
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B78" s="8" t="n"/>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -12536,13 +12536,13 @@
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
     </row>
@@ -13208,15 +13208,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -13226,13 +13226,13 @@
       <c r="A12" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B12" s="8" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -13256,7 +13256,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -13272,15 +13272,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>47</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -13288,15 +13288,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -13304,15 +13304,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -13322,13 +13322,13 @@
       <c r="A18" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B18" s="8" t="n"/>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -13342,7 +13342,7 @@
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -13400,11 +13400,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -13418,15 +13418,15 @@
       <c r="A24" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
@@ -13438,33 +13438,33 @@
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -13480,7 +13480,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -13566,7 +13566,7 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -13576,13 +13576,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -13598,7 +13598,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -13608,13 +13608,13 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -13630,7 +13630,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -13672,15 +13672,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -13688,11 +13688,11 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
@@ -13704,15 +13704,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -13752,13 +13752,13 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -13774,7 +13774,7 @@
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -13784,13 +13784,13 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -13806,43 +13806,43 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B50" s="8" t="n"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -13912,15 +13912,15 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -13930,13 +13930,13 @@
       <c r="A56" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -13950,7 +13950,7 @@
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -13966,7 +13966,7 @@
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -13982,7 +13982,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -13998,7 +13998,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -14008,13 +14008,13 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -14136,31 +14136,31 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -14170,15 +14170,15 @@
       <c r="A71" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
     </row>
@@ -14190,13 +14190,13 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="n"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -14256,7 +14256,7 @@
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G76" s="8" t="n"/>
@@ -14264,17 +14264,17 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -14346,13 +14346,13 @@
       <c r="A82" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="8" t="n"/>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
@@ -14366,7 +14366,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -14380,15 +14380,15 @@
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -14402,39 +14402,39 @@
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="n"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B87" s="8" t="n"/>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>
@@ -14972,15 +14972,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -14988,15 +14988,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B12" s="8" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -15004,7 +15004,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -15020,7 +15020,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -15036,15 +15036,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -15052,15 +15052,15 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -15068,13 +15068,13 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -15090,7 +15090,7 @@
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -15164,11 +15164,11 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -15182,53 +15182,53 @@
       <c r="A24" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -15244,7 +15244,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -15314,7 +15314,7 @@
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -15324,15 +15324,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="8" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -15342,13 +15342,13 @@
       <c r="A34" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -15356,13 +15356,13 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -15378,7 +15378,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -15388,15 +15388,15 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -15406,13 +15406,13 @@
       <c r="A38" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
@@ -15436,15 +15436,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -15454,13 +15454,13 @@
       <c r="A41" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -15468,7 +15468,7 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
@@ -15500,15 +15500,15 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B44" s="8" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
@@ -15518,13 +15518,13 @@
       <c r="A45" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -15538,7 +15538,7 @@
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -15548,13 +15548,13 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -15570,43 +15570,43 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B50" s="8" t="n"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -15676,15 +15676,15 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B55" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -15694,13 +15694,13 @@
       <c r="A56" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -15714,7 +15714,7 @@
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -15730,7 +15730,7 @@
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -15746,7 +15746,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -15762,7 +15762,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -15772,13 +15772,13 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -15900,31 +15900,31 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B70" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -15934,13 +15934,13 @@
       <c r="A71" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -15954,7 +15954,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -15970,7 +15970,7 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -15984,13 +15984,13 @@
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
     </row>
@@ -16002,13 +16002,13 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="n"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -16132,7 +16132,7 @@
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G83" s="8" t="n"/>
@@ -16146,13 +16146,13 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -16166,39 +16166,39 @@
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="n"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B87" s="8" t="n"/>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
     </row>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -924,7 +924,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -956,7 +956,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -1008,35 +1008,35 @@
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -1214,13 +1214,13 @@
       <c r="A33" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -1228,15 +1228,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -1266,7 +1266,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
@@ -1324,15 +1324,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -1342,13 +1342,13 @@
       <c r="A41" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -1598,13 +1598,13 @@
       <c r="A57" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B57" s="8" t="n"/>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -1618,7 +1618,7 @@
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1630,13 +1630,13 @@
       <c r="A59" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -1650,7 +1650,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1666,7 +1666,7 @@
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1676,31 +1676,31 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -1714,7 +1714,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1730,7 +1730,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1746,7 +1746,7 @@
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1756,13 +1756,13 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1772,13 +1772,13 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1788,19 +1788,19 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -1820,15 +1820,15 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B71" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -1838,13 +1838,13 @@
       <c r="A72" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -1886,13 +1886,13 @@
       <c r="A75" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -1906,7 +1906,7 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -1922,7 +1922,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -1938,7 +1938,7 @@
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -1952,13 +1952,13 @@
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C82" s="8" t="n"/>
@@ -2036,7 +2036,7 @@
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G84" s="8" t="n"/>
@@ -2052,7 +2052,7 @@
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G85" s="8" t="n"/>
@@ -2066,13 +2066,13 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -2086,7 +2086,7 @@
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
@@ -2108,19 +2108,19 @@
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C92" s="8" t="n"/>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C93" s="8" t="n"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C95" s="8" t="n"/>
@@ -2752,15 +2752,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -2770,13 +2770,13 @@
       <c r="A20" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B20" s="8" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
@@ -2836,29 +2836,29 @@
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
@@ -2866,13 +2866,13 @@
       <c r="A26" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
@@ -2992,15 +2992,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -3010,13 +3010,13 @@
       <c r="A35" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="8" t="n"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -3030,7 +3030,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -3044,31 +3044,31 @@
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3088,15 +3088,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -3122,13 +3122,13 @@
       <c r="A42" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -3136,15 +3136,15 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -3156,15 +3156,15 @@
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -3188,15 +3188,15 @@
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -3378,13 +3378,13 @@
       <c r="A58" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B58" s="8" t="n"/>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -3398,7 +3398,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -3412,13 +3412,13 @@
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -3442,13 +3442,13 @@
       <c r="A62" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -3458,15 +3458,15 @@
       <c r="A63" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
@@ -3476,13 +3476,13 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
     </row>
@@ -3494,77 +3494,77 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -3578,7 +3578,7 @@
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
@@ -3618,13 +3618,13 @@
       <c r="A73" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
@@ -3632,15 +3632,15 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C76" s="8" t="n"/>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C77" s="8" t="n"/>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -3714,13 +3714,13 @@
       <c r="A79" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B79" s="8" t="n"/>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -3734,7 +3734,7 @@
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -3750,7 +3750,7 @@
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -3766,7 +3766,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -3776,15 +3776,15 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
@@ -3814,7 +3814,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -3958,7 +3958,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -3974,7 +3974,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -4038,7 +4038,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -4054,7 +4054,7 @@
       <c r="C100" s="8" t="n"/>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -4064,13 +4064,13 @@
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
@@ -4326,13 +4326,13 @@
       <c r="A7" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -4340,15 +4340,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -4516,15 +4516,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -4534,13 +4534,13 @@
       <c r="A20" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B20" s="8" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -4580,15 +4580,15 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -4598,13 +4598,13 @@
       <c r="A24" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -4618,7 +4618,7 @@
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -4692,7 +4692,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -4808,43 +4808,43 @@
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -4858,7 +4858,7 @@
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -4886,13 +4886,13 @@
       <c r="A42" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -4900,15 +4900,15 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -4920,15 +4920,15 @@
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -4952,15 +4952,15 @@
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -5142,13 +5142,13 @@
       <c r="A58" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B58" s="8" t="n"/>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -5162,7 +5162,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -5176,13 +5176,13 @@
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -5206,13 +5206,13 @@
       <c r="A62" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -5222,15 +5222,15 @@
       <c r="A63" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
@@ -5240,13 +5240,13 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
     </row>
@@ -5258,77 +5258,77 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -5342,7 +5342,7 @@
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
@@ -5382,13 +5382,13 @@
       <c r="A73" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
@@ -5396,15 +5396,15 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
@@ -5418,7 +5418,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -5428,15 +5428,15 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -5444,15 +5444,15 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -5478,13 +5478,13 @@
       <c r="A79" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B79" s="8" t="n"/>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -5494,13 +5494,13 @@
       <c r="A80" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B80" s="8" t="n"/>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
@@ -5510,13 +5510,13 @@
       <c r="A81" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B81" s="8" t="n"/>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -5530,7 +5530,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -5540,15 +5540,15 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
@@ -5556,15 +5556,15 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
@@ -5572,13 +5572,13 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -5590,13 +5590,13 @@
       <c r="A86" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B86" s="8" t="n"/>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
@@ -5610,7 +5610,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -5738,7 +5738,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -5754,7 +5754,7 @@
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -5786,7 +5786,7 @@
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -5800,31 +5800,31 @@
       </c>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -5850,7 +5850,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -6216,15 +6216,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -6234,13 +6234,13 @@
       <c r="A16" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B16" s="8" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -6248,7 +6248,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -6280,15 +6280,15 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -6298,13 +6298,13 @@
       <c r="A20" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B20" s="8" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -6344,7 +6344,7 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
@@ -6364,29 +6364,29 @@
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
@@ -6394,13 +6394,13 @@
       <c r="A26" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -6456,7 +6456,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -6572,31 +6572,31 @@
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -6606,7 +6606,7 @@
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -6650,13 +6650,13 @@
       <c r="A42" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -6666,13 +6666,13 @@
       <c r="A43" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -6684,15 +6684,15 @@
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -6716,15 +6716,15 @@
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -6764,29 +6764,29 @@
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -6846,7 +6846,7 @@
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -6862,7 +6862,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -6872,15 +6872,15 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
@@ -6888,17 +6888,17 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
     </row>
@@ -6910,7 +6910,7 @@
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -6924,29 +6924,29 @@
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -6970,13 +6970,13 @@
       <c r="A62" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -6988,13 +6988,13 @@
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
     </row>
@@ -7004,13 +7004,13 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
     </row>
@@ -7022,109 +7022,109 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
-      <c r="H70" s="8" t="n"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B71" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -7146,13 +7146,13 @@
       <c r="A73" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
@@ -7160,15 +7160,15 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -7310,7 +7310,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -7486,7 +7486,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -7502,7 +7502,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -7566,7 +7566,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -7582,7 +7582,7 @@
       <c r="C100" s="8" t="n"/>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -7598,7 +7598,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -7608,13 +7608,13 @@
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -8012,7 +8012,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -8220,7 +8220,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -8348,13 +8348,13 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
@@ -8510,13 +8510,13 @@
       <c r="A48" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B48" s="8" t="n"/>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -8530,7 +8530,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -8544,29 +8544,29 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C54" s="8" t="n"/>
@@ -8636,19 +8636,19 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -8656,15 +8656,15 @@
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -8734,13 +8734,13 @@
       <c r="A62" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B62" s="8" t="n"/>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -8754,7 +8754,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -8770,7 +8770,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -8786,7 +8786,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -8800,13 +8800,13 @@
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -8830,13 +8830,13 @@
       <c r="A68" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -8846,13 +8846,13 @@
       <c r="A69" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -8866,7 +8866,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -8882,7 +8882,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -8896,13 +8896,13 @@
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="n"/>
     </row>
@@ -8912,13 +8912,13 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -8930,13 +8930,13 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -8946,73 +8946,73 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="n"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B76" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B77" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B78" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -9022,15 +9022,15 @@
       <c r="A80" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B80" s="8" t="n"/>
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
-      <c r="F80" s="8" t="n"/>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G80" s="8" t="n"/>
       <c r="H80" s="8" t="n"/>
     </row>
@@ -9040,27 +9040,27 @@
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B82" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
@@ -9070,13 +9070,13 @@
       <c r="A83" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
@@ -9086,13 +9086,13 @@
       <c r="A84" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
@@ -9100,15 +9100,15 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -9116,13 +9116,13 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -9138,7 +9138,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C88" s="8" t="n"/>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -9198,13 +9198,13 @@
       <c r="A91" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B91" s="8" t="n"/>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -9218,7 +9218,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -9234,7 +9234,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -9250,7 +9250,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -9266,7 +9266,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -9276,15 +9276,15 @@
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
@@ -9776,7 +9776,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -9888,7 +9888,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
@@ -9984,7 +9984,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -10002,13 +10002,13 @@
       <c r="A31" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -10016,15 +10016,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -10102,7 +10102,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -10112,13 +10112,13 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
@@ -10176,7 +10176,7 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
@@ -10274,13 +10274,13 @@
       <c r="A48" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B48" s="8" t="n"/>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -10294,7 +10294,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -10308,29 +10308,29 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -10372,7 +10372,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C54" s="8" t="n"/>
@@ -10400,19 +10400,19 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -10420,15 +10420,15 @@
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -10498,13 +10498,13 @@
       <c r="A62" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="8" t="n"/>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
@@ -10518,7 +10518,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -10534,7 +10534,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -10550,7 +10550,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -10564,13 +10564,13 @@
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -10642,13 +10642,13 @@
       <c r="A71" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -10662,7 +10662,7 @@
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -10678,7 +10678,7 @@
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -10694,7 +10694,7 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -10710,7 +10710,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -10724,13 +10724,13 @@
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
     </row>
@@ -10740,13 +10740,13 @@
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
     </row>
@@ -10774,13 +10774,13 @@
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -10794,7 +10794,7 @@
       <c r="G80" s="8" t="n"/>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
@@ -10816,31 +10816,31 @@
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B82" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
@@ -10850,13 +10850,13 @@
       <c r="A84" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
@@ -10864,15 +10864,15 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -10880,13 +10880,13 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -10902,7 +10902,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C88" s="8" t="n"/>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -10962,13 +10962,13 @@
       <c r="A91" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="8" t="n"/>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -10982,7 +10982,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -10998,7 +10998,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -11014,7 +11014,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -11030,7 +11030,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -11040,15 +11040,15 @@
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
@@ -11540,7 +11540,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -11652,7 +11652,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
@@ -11748,7 +11748,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -11766,13 +11766,13 @@
       <c r="A31" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -11780,15 +11780,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="8" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -11866,7 +11866,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -11876,13 +11876,13 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
@@ -12038,13 +12038,13 @@
       <c r="A48" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B48" s="8" t="n"/>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
@@ -12058,7 +12058,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -12072,29 +12072,29 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C54" s="8" t="n"/>
@@ -12164,19 +12164,19 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -12184,15 +12184,15 @@
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -12246,13 +12246,13 @@
       <c r="A61" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="8" t="n"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -12266,7 +12266,7 @@
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -12282,7 +12282,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -12298,7 +12298,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -12312,13 +12312,13 @@
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
@@ -12332,7 +12332,7 @@
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G66" s="8" t="n"/>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -12358,13 +12358,13 @@
       <c r="A68" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
@@ -12374,13 +12374,13 @@
       <c r="A69" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -12394,7 +12394,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -12410,7 +12410,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -12424,13 +12424,13 @@
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="n"/>
     </row>
@@ -12440,13 +12440,13 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -12458,73 +12458,73 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B75" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B76" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B77" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -12534,15 +12534,15 @@
       <c r="A79" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="n"/>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
     </row>
@@ -12552,15 +12552,15 @@
       </c>
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
-      <c r="H80" s="8" t="n"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -12568,43 +12568,43 @@
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B82" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
@@ -12614,13 +12614,13 @@
       <c r="A84" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
@@ -12628,15 +12628,15 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B85" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -12644,15 +12644,15 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B86" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
@@ -12730,7 +12730,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -12746,7 +12746,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -12762,7 +12762,7 @@
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -12778,7 +12778,7 @@
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -12794,7 +12794,7 @@
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -12804,15 +12804,15 @@
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
@@ -13208,11 +13208,11 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -13256,7 +13256,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -13562,13 +13562,13 @@
       <c r="A33" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -13576,15 +13576,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -13614,7 +13614,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -13624,13 +13624,13 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -13694,7 +13694,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -13704,13 +13704,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -13912,7 +13912,7 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -13946,13 +13946,13 @@
       <c r="A57" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B57" s="8" t="n"/>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -13966,7 +13966,7 @@
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -13978,13 +13978,13 @@
       <c r="A59" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -13996,25 +13996,25 @@
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -14030,7 +14030,7 @@
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -14046,7 +14046,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -14062,7 +14062,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -14072,15 +14072,15 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B65" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
@@ -14088,31 +14088,31 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -14126,7 +14126,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -14136,13 +14136,13 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -14168,15 +14168,15 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B71" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -14186,13 +14186,13 @@
       <c r="A72" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -14220,7 +14220,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -14234,13 +14234,13 @@
       <c r="A75" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -14254,7 +14254,7 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -14270,7 +14270,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -14280,13 +14280,13 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -14296,27 +14296,27 @@
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -14328,65 +14328,65 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
-      <c r="F81" s="8" t="n"/>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B84" s="8" t="n"/>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
     </row>
@@ -14398,77 +14398,77 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B86" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B87" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -14508,7 +14508,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C92" s="8" t="n"/>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C93" s="8" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C95" s="8" t="n"/>
@@ -15036,7 +15036,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -15052,7 +15052,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -15378,7 +15378,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -15394,7 +15394,7 @@
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -15404,7 +15404,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -15420,7 +15420,7 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
@@ -15436,15 +15436,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -15454,13 +15454,13 @@
       <c r="A41" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -15676,7 +15676,7 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -15710,13 +15710,13 @@
       <c r="A57" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="8" t="n"/>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -15730,7 +15730,7 @@
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -15742,13 +15742,13 @@
       <c r="A59" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -15762,7 +15762,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -15778,7 +15778,7 @@
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -15788,31 +15788,31 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -15826,7 +15826,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -15842,7 +15842,7 @@
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -15856,27 +15856,27 @@
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -15890,7 +15890,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -15906,7 +15906,7 @@
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -15916,7 +15916,7 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
@@ -15932,7 +15932,7 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
@@ -16046,13 +16046,13 @@
       <c r="A78" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B78" s="8" t="n"/>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -16064,13 +16064,13 @@
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
     </row>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -16110,15 +16110,15 @@
       <c r="A82" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
     </row>
@@ -16126,15 +16126,15 @@
       <c r="A83" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
     </row>
@@ -16146,13 +16146,13 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -16162,77 +16162,77 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B86" s="8" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B87" s="8" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C92" s="8" t="n"/>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C93" s="8" t="n"/>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C95" s="8" t="n"/>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -844,7 +844,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -910,13 +910,13 @@
       <c r="A14" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -924,15 +924,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -940,7 +940,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -956,11 +956,11 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -990,13 +990,13 @@
       <c r="A19" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -1020,15 +1020,15 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B21" s="8" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -1036,7 +1036,7 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1196,13 +1196,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1214,13 +1214,13 @@
       <c r="A33" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="8" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -1228,15 +1228,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -1314,7 +1314,7 @@
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1324,15 +1324,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -1342,13 +1342,13 @@
       <c r="A41" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1468,17 +1468,17 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -1518,13 +1518,13 @@
       <c r="A52" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -1538,7 +1538,7 @@
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1552,13 +1552,13 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
@@ -1634,7 +1634,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1650,7 +1650,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1666,7 +1666,7 @@
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1680,43 +1680,43 @@
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B64" s="8" t="n"/>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -1746,7 +1746,7 @@
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1756,13 +1756,13 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1772,13 +1772,13 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1820,15 +1820,15 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -1838,13 +1838,13 @@
       <c r="A72" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B72" s="8" t="n"/>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -1998,15 +1998,15 @@
       <c r="A82" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
     </row>
@@ -2014,15 +2014,15 @@
       <c r="A83" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
     </row>
@@ -2034,13 +2034,13 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -2050,77 +2050,77 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B86" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B87" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B88" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B89" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C91" s="8" t="n"/>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C92" s="8" t="n"/>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C93" s="8" t="n"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C94" s="8" t="n"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C95" s="8" t="n"/>
@@ -2222,13 +2222,13 @@
       <c r="A96" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
@@ -2238,13 +2238,13 @@
       <c r="A97" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="n"/>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
@@ -2258,7 +2258,7 @@
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2274,7 +2274,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2290,7 +2290,7 @@
       <c r="C100" s="8" t="n"/>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2304,13 +2304,13 @@
       </c>
       <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
-      <c r="F101" s="8" t="n"/>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="n"/>
     </row>
@@ -2320,13 +2320,13 @@
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="n"/>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
     </row>
@@ -2338,13 +2338,13 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
-      <c r="H103" s="8" t="n"/>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -2562,13 +2562,13 @@
       <c r="A7" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -2576,15 +2576,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -2592,11 +2592,11 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
@@ -2610,13 +2610,13 @@
       <c r="A10" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="B10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -2624,15 +2624,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -2642,13 +2642,13 @@
       <c r="A12" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -2672,15 +2672,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B14" s="8" t="n"/>
+        <v>47</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
@@ -2836,29 +2836,29 @@
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
@@ -2866,13 +2866,13 @@
       <c r="A26" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -2992,15 +2992,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -3010,13 +3010,13 @@
       <c r="A35" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -3248,17 +3248,17 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B50" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -3314,13 +3314,13 @@
       <c r="A54" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -3334,7 +3334,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -3348,13 +3348,13 @@
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
     </row>
@@ -3654,7 +3654,7 @@
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -3664,15 +3664,15 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C77" s="8" t="n"/>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -3730,13 +3730,13 @@
       <c r="A80" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B80" s="8" t="n"/>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
@@ -3814,7 +3814,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -3830,7 +3830,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -3846,7 +3846,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -3860,13 +3860,13 @@
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
     </row>
@@ -3878,13 +3878,13 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -3898,7 +3898,7 @@
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -3914,37 +3914,37 @@
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B92" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
@@ -4064,13 +4064,13 @@
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -4086,7 +4086,7 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -4340,11 +4340,11 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
@@ -4372,15 +4372,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -4388,15 +4388,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -4406,13 +4406,13 @@
       <c r="A12" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -4420,13 +4420,13 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -4436,15 +4436,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B14" s="8" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
@@ -4580,15 +4580,15 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B23" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -4598,13 +4598,13 @@
       <c r="A24" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -4618,7 +4618,7 @@
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -4692,7 +4692,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
@@ -5012,17 +5012,17 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B50" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -5078,13 +5078,13 @@
       <c r="A54" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -5098,7 +5098,7 @@
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -5112,13 +5112,13 @@
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
     </row>
@@ -5434,7 +5434,7 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -5444,15 +5444,15 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B77" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -5510,13 +5510,13 @@
       <c r="A81" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -5530,7 +5530,7 @@
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -5546,7 +5546,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -5556,15 +5556,15 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B84" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
@@ -5572,13 +5572,13 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -5590,13 +5590,13 @@
       <c r="A86" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
@@ -5610,7 +5610,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -5624,13 +5624,13 @@
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
     </row>
@@ -5642,13 +5642,13 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -5662,7 +5662,7 @@
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -5678,25 +5678,25 @@
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B92" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C93" s="8" t="n"/>
@@ -5718,13 +5718,13 @@
       <c r="A94" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B94" s="8" t="n"/>
       <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E94" s="8" t="n"/>
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="8" t="n"/>
@@ -5786,7 +5786,7 @@
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -5800,31 +5800,31 @@
       </c>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="n"/>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -5834,7 +5834,7 @@
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -5844,13 +5844,13 @@
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -6090,13 +6090,13 @@
       <c r="A7" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -6104,15 +6104,15 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B8" s="8" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
@@ -6136,15 +6136,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -6152,13 +6152,13 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -6168,15 +6168,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -6186,13 +6186,13 @@
       <c r="A13" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -6200,15 +6200,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B14" s="8" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -6218,13 +6218,13 @@
       <c r="A15" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B15" s="8" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -6234,13 +6234,13 @@
       <c r="A16" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -6248,7 +6248,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
@@ -6364,29 +6364,29 @@
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
@@ -6394,13 +6394,13 @@
       <c r="A26" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -6456,7 +6456,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
@@ -6760,15 +6760,15 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -6776,17 +6776,17 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B50" s="8" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -6826,13 +6826,13 @@
       <c r="A53" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -6872,33 +6872,33 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
     </row>
@@ -6906,13 +6906,13 @@
       <c r="A58" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B58" s="8" t="n"/>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -6936,17 +6936,17 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -6954,13 +6954,13 @@
       <c r="A61" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -7310,7 +7310,7 @@
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -7326,7 +7326,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -7342,7 +7342,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -7358,7 +7358,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -7374,7 +7374,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -7388,13 +7388,13 @@
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
     </row>
@@ -7406,13 +7406,13 @@
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -7426,7 +7426,7 @@
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -7442,37 +7442,37 @@
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B92" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
@@ -7900,15 +7900,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -7916,15 +7916,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -7948,11 +7948,11 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C13" s="8" t="n"/>
@@ -7964,15 +7964,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -7980,15 +7980,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -7998,13 +7998,13 @@
       <c r="A16" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -8012,15 +8012,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -8236,15 +8236,15 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -8254,13 +8254,13 @@
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="n"/>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
@@ -8556,17 +8556,17 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -8606,13 +8606,13 @@
       <c r="A54" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -8624,13 +8624,13 @@
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -8720,29 +8720,29 @@
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
@@ -8750,13 +8750,13 @@
       <c r="A63" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -8796,15 +8796,15 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -8814,13 +8814,13 @@
       <c r="A67" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -9100,15 +9100,15 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -9118,13 +9118,13 @@
       <c r="A86" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B86" s="8" t="n"/>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
@@ -9138,7 +9138,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
@@ -9664,15 +9664,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>59</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -9680,15 +9680,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -9712,11 +9712,11 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C13" s="8" t="n"/>
@@ -9728,15 +9728,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -9744,15 +9744,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -9762,13 +9762,13 @@
       <c r="A16" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -9776,15 +9776,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -9808,7 +9808,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
@@ -9984,7 +9984,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
@@ -10016,7 +10016,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
@@ -10320,17 +10320,17 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -10370,13 +10370,13 @@
       <c r="A54" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -10388,13 +10388,13 @@
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -10484,29 +10484,29 @@
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
     </row>
@@ -10514,13 +10514,13 @@
       <c r="A63" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -10560,15 +10560,15 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -10626,13 +10626,13 @@
       <c r="A70" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
@@ -10864,15 +10864,15 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -10882,13 +10882,13 @@
       <c r="A86" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="8" t="n"/>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
@@ -10902,7 +10902,7 @@
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
@@ -11428,15 +11428,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B10" s="8" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -11444,15 +11444,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -11476,11 +11476,11 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C13" s="8" t="n"/>
@@ -11492,15 +11492,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -11508,15 +11508,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -11526,13 +11526,13 @@
       <c r="A16" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
@@ -11540,15 +11540,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -11572,7 +11572,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
@@ -11748,7 +11748,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
@@ -11780,7 +11780,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
@@ -12084,17 +12084,17 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B51" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -12134,13 +12134,13 @@
       <c r="A54" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -12152,13 +12152,13 @@
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -12312,29 +12312,29 @@
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B66" s="8" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
     </row>
@@ -12342,13 +12342,13 @@
       <c r="A67" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -12628,15 +12628,15 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C86" s="8" t="n"/>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C87" s="8" t="n"/>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C88" s="8" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C89" s="8" t="n"/>
@@ -12710,13 +12710,13 @@
       <c r="A90" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B90" s="8" t="n"/>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
@@ -12730,7 +12730,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -13192,11 +13192,11 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -13258,13 +13258,13 @@
       <c r="A14" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -13272,15 +13272,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>47</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -13288,7 +13288,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -13304,11 +13304,11 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -13338,43 +13338,43 @@
       <c r="A19" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -13384,15 +13384,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B22" s="8" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -13512,7 +13512,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -13544,13 +13544,13 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -13562,13 +13562,13 @@
       <c r="A33" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="8" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -13576,15 +13576,15 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
@@ -13694,7 +13694,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -13704,13 +13704,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -13816,17 +13816,17 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -13866,13 +13866,13 @@
       <c r="A52" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -13886,7 +13886,7 @@
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -13900,19 +13900,19 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
@@ -13982,7 +13982,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -13996,25 +13996,25 @@
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -14024,13 +14024,13 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -14040,19 +14040,19 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -14062,7 +14062,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -14072,15 +14072,15 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
@@ -14090,13 +14090,13 @@
       <c r="A66" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
@@ -14110,7 +14110,7 @@
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -14126,7 +14126,7 @@
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -14136,7 +14136,7 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
@@ -14168,15 +14168,15 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -14186,13 +14186,13 @@
       <c r="A72" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="8" t="n"/>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -14220,7 +14220,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -14234,13 +14234,13 @@
       <c r="A75" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+      <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -14254,7 +14254,7 @@
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -14270,7 +14270,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -14280,15 +14280,15 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B78" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
@@ -14296,13 +14296,13 @@
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -14312,7 +14312,7 @@
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
@@ -14328,23 +14328,23 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B81" s="8" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
@@ -14352,7 +14352,7 @@
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G82" s="8" t="n"/>
@@ -14360,35 +14360,35 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -14942,13 +14942,13 @@
       <c r="A9" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B9" s="8" t="n"/>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -14956,15 +14956,15 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -15022,13 +15022,13 @@
       <c r="A14" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -15036,15 +15036,15 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B15" s="8" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -15068,11 +15068,11 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
@@ -15118,13 +15118,13 @@
       <c r="A20" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -15132,13 +15132,13 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -15148,15 +15148,15 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B22" s="8" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
@@ -15276,7 +15276,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
@@ -15324,7 +15324,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -15404,7 +15404,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
@@ -15426,7 +15426,7 @@
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -15436,15 +15436,15 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -15454,13 +15454,13 @@
       <c r="A41" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -15580,17 +15580,17 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B49" s="8" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -15630,13 +15630,13 @@
       <c r="A52" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -15650,7 +15650,7 @@
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -15664,19 +15664,19 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
@@ -15746,7 +15746,7 @@
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -15762,7 +15762,7 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -15778,7 +15778,7 @@
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -15792,43 +15792,43 @@
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="8" t="n"/>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
@@ -15916,7 +15916,7 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
@@ -15932,7 +15932,7 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>

--- a/TradeValueSheets/TradeValues_AllCombinations.xlsx
+++ b/TradeValueSheets/TradeValues_AllCombinations.xlsx
@@ -764,7 +764,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -828,15 +828,15 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
+        <v>62</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -846,13 +846,13 @@
       <c r="A10" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -892,7 +892,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -908,11 +908,11 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -940,11 +940,11 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -956,15 +956,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -976,29 +976,29 @@
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
@@ -1010,7 +1010,7 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -1068,15 +1068,15 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -1088,31 +1088,31 @@
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1120,29 +1120,29 @@
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B28" s="8" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
     </row>
@@ -1150,13 +1150,13 @@
       <c r="A29" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -1196,15 +1196,15 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
@@ -1212,15 +1212,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -1228,13 +1228,13 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1244,15 +1244,15 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -1298,7 +1298,7 @@
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1326,13 +1326,13 @@
       <c r="A40" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
@@ -1388,11 +1388,11 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
@@ -1410,7 +1410,7 @@
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1422,13 +1422,13 @@
       <c r="A46" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
@@ -1438,13 +1438,13 @@
       <c r="A47" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -1452,13 +1452,13 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1470,25 +1470,25 @@
       <c r="A49" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -1500,11 +1500,11 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -1516,15 +1516,15 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
@@ -1532,17 +1532,17 @@
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
     </row>
@@ -1552,35 +1552,35 @@
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C58" s="8" t="n"/>
@@ -1630,13 +1630,13 @@
       <c r="A59" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -1644,15 +1644,15 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B60" s="8" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -1838,13 +1838,13 @@
       <c r="A72" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -1856,13 +1856,13 @@
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
     </row>
@@ -1874,29 +1874,29 @@
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B75" s="8" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C76" s="8" t="n"/>
@@ -2546,13 +2546,13 @@
       <c r="A6" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -2560,15 +2560,15 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B7" s="8" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -2614,7 +2614,7 @@
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -2624,15 +2624,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B11" s="8" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -2640,15 +2640,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -2674,13 +2674,13 @@
       <c r="A14" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -2720,43 +2720,43 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B18" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -2768,11 +2768,11 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
@@ -2804,29 +2804,29 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B23" s="8" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
     </row>
@@ -2834,13 +2834,13 @@
       <c r="A24" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -2852,29 +2852,29 @@
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -2882,13 +2882,13 @@
       <c r="A27" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -2976,15 +2976,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -2992,11 +2992,11 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C34" s="8" t="n"/>
@@ -3008,19 +3008,19 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3030,7 +3030,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -3044,15 +3044,15 @@
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3104,15 +3104,15 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B41" s="8" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -3158,7 +3158,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -3168,13 +3168,13 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -3204,43 +3204,43 @@
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B48" s="8" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -3252,31 +3252,31 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -3314,13 +3314,13 @@
       <c r="A54" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B54" s="8" t="n"/>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -3330,15 +3330,15 @@
       <c r="A55" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -3346,15 +3346,15 @@
       <c r="A56" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B56" s="8" t="n"/>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
     </row>
@@ -3364,27 +3364,27 @@
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -3392,15 +3392,15 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -3408,17 +3408,17 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
     </row>
@@ -3476,13 +3476,13 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
     </row>
@@ -3496,7 +3496,7 @@
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G65" s="8" t="n"/>
@@ -3512,7 +3512,7 @@
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G66" s="8" t="n"/>
@@ -3520,35 +3520,35 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="n"/>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -3574,7 +3574,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -3588,27 +3588,27 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="n"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B72" s="8" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -3616,19 +3616,19 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -4356,13 +4356,13 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -4378,7 +4378,7 @@
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -4388,15 +4388,15 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B11" s="8" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -4404,15 +4404,15 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
@@ -4438,13 +4438,13 @@
       <c r="A14" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -4484,15 +4484,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -4516,11 +4516,11 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -4532,11 +4532,11 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
@@ -4616,29 +4616,29 @@
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
@@ -4646,13 +4646,13 @@
       <c r="A27" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -4692,7 +4692,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -4740,15 +4740,15 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -4756,35 +4756,35 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B34" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -4868,11 +4868,11 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
@@ -4884,15 +4884,15 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B42" s="8" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
@@ -4922,7 +4922,7 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -4932,13 +4932,13 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -4968,45 +4968,45 @@
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
     </row>
@@ -5016,15 +5016,15 @@
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -5078,13 +5078,13 @@
       <c r="A54" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B54" s="8" t="n"/>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
@@ -5094,15 +5094,15 @@
       <c r="A55" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
     </row>
@@ -5110,15 +5110,15 @@
       <c r="A56" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B56" s="8" t="n"/>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
     </row>
@@ -5128,27 +5128,27 @@
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
@@ -5156,17 +5156,17 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
     </row>
@@ -5240,13 +5240,13 @@
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
     </row>
@@ -5260,7 +5260,7 @@
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G65" s="8" t="n"/>
@@ -5276,7 +5276,7 @@
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G66" s="8" t="n"/>
@@ -5284,35 +5284,35 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="n"/>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -5338,7 +5338,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -5352,27 +5352,27 @@
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="n"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B72" s="8" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
@@ -5380,19 +5380,19 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -6056,7 +6056,7 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -6136,13 +6136,13 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
@@ -6168,13 +6168,13 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -6200,15 +6200,15 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -6248,15 +6248,15 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B17" s="8" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -6280,11 +6280,11 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -6296,15 +6296,15 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B20" s="8" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
@@ -6312,15 +6312,15 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -6360,7 +6360,7 @@
     </row>